--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,5533 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>22990668</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447427529818</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46220.02149305555</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46220.02150462963</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1fe94b7f-2221-4396-9da1-eff6c32dd545              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f15bf356-9c37-4bbc-b831-7dcae2d687cd              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 246 556</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>22990667</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5541984417815</v>
+      </c>
+      <c r="F3" t="n">
+        <v>724</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OI MOVEL S.A. - (BRASILTELECOM)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>CLICKSMS</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46220.02131944444</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46220.02133101852</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46220.02148148148</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57b09bc0-f74c-4a70-8002-bb84f5cf6ba3              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bec7acf8-a069-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>MQL5 code: 6753</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>22990666</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447309845957</v>
+      </c>
+      <c r="F4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46220.01997685185</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46220.01998842593</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46220.02005787037</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6c232e5f-51ef-469c-8292-d1444abec836              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2d80e3d5-60a5-45ed-9d9f-068078227247              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hi there. 614 994</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>22990665</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>51919129262</v>
+      </c>
+      <c r="F5" t="n">
+        <v>716</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46220.01984953704</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46220.01991898148</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46220.01993055556</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c7a0a5ad-c609-43d1-bfb8-992f0f393b53              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baa898d6-a4ad-43d3-b557-a56910da5e2e              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 1766
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>22990664</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>447715549527</v>
+      </c>
+      <c r="F6" t="n">
+        <v>234</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46220.01924768519</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46220.01927083333</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46220.01943287037</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1fc3127f-7e51-4dce-b0e6-48a95b613b8f              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f0380a22-8431-4e5a-ad1c-b530783a2546              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Hi there. 709 256</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>22990663</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>447400413291</v>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46220.0190162037</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46220.01903935185</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46220.01909722222</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24cb4dc9-e645-407b-b8ad-15405f506c95              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b690863f-5c05-4f6c-8e58-977cea1a6a80              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hi there. 640 453</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>22990662</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447492040728</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46220.01827546296</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46220.01829861111</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46220.01834490741</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4d731165-a2f1-456e-b666-d76e52546fb5              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3d3b109c-978f-4aed-abc5-897e3656abce              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 799 092</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>22990661</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447365530126</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46220.01730324074</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46220.01731481482</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46220.01737268519</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b2c153ed-2743-41bd-b31c-6df0391f5bc8              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9a2f1ee2-81c6-4c08-a72e-c5a4573ddba2              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 696 601</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>22990660</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>447874305002</v>
+      </c>
+      <c r="F10" t="n">
+        <v>234</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46220.01668981482</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46220.01671296296</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46220.01690972222</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">af4f25f6-72cf-415e-9a7a-0d2c2ee3730b              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c662ff15-3b1c-4399-b9fe-257f348fd42e              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Hi there. 236 550</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>22990659</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>447720109591</v>
+      </c>
+      <c r="F11" t="n">
+        <v>234</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46220.01655092592</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46220.01657407408</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46220.01678240741</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3ba784f-a465-4086-935d-0868b64507af              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240dc148-08e8-46b0-b4ae-26b7a73fa6e1              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Hi there. 210 346</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>22990658</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447586431129</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46220.01644675926</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46220.01646990741</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46220.01652777778</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fd083a23-4249-407b-9382-2dbda6231bc6              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ee7b359b-d6e0-4f8a-91d3-c2315a2b4079              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 324 046</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>22990657</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>447575050607</v>
+      </c>
+      <c r="F13" t="n">
+        <v>234</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46220.01540509259</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46220.01541666667</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46220.01547453704</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ae9ded58-b8e3-4c62-ad66-526ce0e8959b              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1f001446-e3f0-47aa-997b-c9c7affe5571              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Hi there. 870 717</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>22990656</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>447988050437</v>
+      </c>
+      <c r="F14" t="n">
+        <v>234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46220.01509259259</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46220.01511574074</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46220.01533564815</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">313886dc-92fb-4413-9e04-13c9a0a47501              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c9f27327-2b5c-47df-8614-c2a6b2b8744e              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Hi there. 396 847</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>22990655</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>447907558524</v>
+      </c>
+      <c r="F15" t="n">
+        <v>234</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46220.01459490741</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46220.01460648148</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46220.0146875</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c72893f3-45c7-4b31-8481-e7e40061ca4d              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eb00bbb5-e95d-4ad0-b678-8bceb6e310f4              </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Hi there. 458 607</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>8 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>22990654</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>447403417889</v>
+      </c>
+      <c r="F16" t="n">
+        <v>234</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46220.01425925926</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46220.01430555555</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46220.014375</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ef09d93a-af33-45cb-9ea7-966ab5e7f931              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dfd90aa4-5bf4-4f8d-a467-eec0917e817f              </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Hi there. 409 747</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22990653</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>447943062848</v>
+      </c>
+      <c r="F17" t="n">
+        <v>234</v>
+      </c>
+      <c r="G17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46220.01365740741</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46220.01369212963</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46220.01375</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e1a1e83c-412d-4c1d-867b-8b7a087d6239              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c0a523e8-77b0-46d2-8d79-6d04355dda84              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Hi there. 066 869</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>8 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>22990652</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>447429389351</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46220.01324074074</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46220.01326388889</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46220.0134375</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4f221d95-d15e-4092-aabf-2ff77c1aa393              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64b828ce-217b-40ae-a32a-baa4e78a385d              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Hi there. 595 678</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>22990651</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>447897792138</v>
+      </c>
+      <c r="F19" t="n">
+        <v>234</v>
+      </c>
+      <c r="G19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46220.01289351852</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46220.01291666667</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46220.01297453704</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6d5551ea-93f6-4eb6-8a01-578ed3912ea8              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14ab4c13-9fa4-44b5-be38-3e367d2d68d5              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Hi there. 267 201</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>22990650</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>447950411763</v>
+      </c>
+      <c r="F20" t="n">
+        <v>234</v>
+      </c>
+      <c r="G20" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46220.01273148148</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46220.01274305556</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46220.0128125</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6a1425d5-e3de-415e-935e-8945f10191af              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90343d82-659d-4662-ab8b-dc449c8e4f21              </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Hi there. 997 393</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>22990649</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>447888107753</v>
+      </c>
+      <c r="F21" t="n">
+        <v>234</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46220.01269675926</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46220.01270833334</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46220.01282407407</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b77d08a0-d1a9-478f-89c0-1fa51d41b363              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21a3565a-09f8-4fcd-8dd6-9386ba54b48e              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Hi there. 976 749</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>22990648</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>447897507262</v>
+      </c>
+      <c r="F22" t="n">
+        <v>234</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46220.01237268518</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46220.01239583334</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46220.0124537037</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a8de2182-e9bf-4aa1-bcac-4f27f6067567              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5bc2dedf-2442-4eb6-904e-f0620801cc67              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Hi there. 396 606</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22990647</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>447888107753</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46220.01171296297</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46220.01173611111</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>46220.0118287037</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93fcc3d5-9d18-4ef4-8091-ae42e6d7e3f0              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ba91aaa6-d656-48c9-a09f-ab8165c44ea0              </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Hi there. 174 368</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22990646</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>447748552099</v>
+      </c>
+      <c r="F24" t="n">
+        <v>234</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46220.0109837963</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46220.01099537037</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46220.0112037037</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1fac7f54-a060-413b-88b7-96f845ff0c9f              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8c92f338-5ee2-42f3-9633-a0680e72120c              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Hi there. 498 051</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22990645</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>447459969948</v>
+      </c>
+      <c r="F25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G25" t="n">
+        <v>26</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Lycamobile UK Limited</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46220.010625</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46220.01065972223</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46220.01074074074</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6c59f0d3-11bc-4a56-a7f9-e7e6b76afa04              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ba19fd89-34eb-4d9a-805b-d52c59ba775f              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Hi there. 716 739</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>22990644</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5513988487557</v>
+      </c>
+      <c r="F26" t="n">
+        <v>724</v>
+      </c>
+      <c r="G26" t="n">
+        <v>31</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>OI S.A. (TNL PCS S.A.)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46220.01060185185</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46220.01063657407</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>46220.01084490741</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33a1fa1f-3cd8-4e26-ac27-d627258c6615              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98050b6c-a067-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Use o seu codigo unico do eneba.com: 727883</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22990643</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>447876555543</v>
+      </c>
+      <c r="F27" t="n">
+        <v>234</v>
+      </c>
+      <c r="G27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46220.01053240741</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46220.01055555556</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46220.01064814815</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a698fdbc-858e-4332-bc89-d212da3430e3              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1616173f-9032-439a-9a49-0805259316a4              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Hi there. 261 157</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>22990642</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>855886239999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>456</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Metfone (Beeline)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46220.01002314815</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46220.01003472223</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46220.01017361111</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d108921b-66cf-4f46-aa0d-f9e8ef9ee47f              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78b72e98-a067-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Your verification code is 6803, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>22990641</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>447877418054</v>
+      </c>
+      <c r="F29" t="n">
+        <v>234</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>46220.00828703704</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>46220.00829861111</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>46220.00835648148</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66e7ebb0-e8b2-4330-a9af-fa2deaed2a99              </t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7c3ade3d-6a53-4390-9bd1-a628055146ec              </t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Hi there. 311 746</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>22990640</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>447473681362</v>
+      </c>
+      <c r="F30" t="n">
+        <v>234</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>46220.00761574074</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>46220.00763888889</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>46220.00769675926</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f20ed678-18fd-4d11-bc9f-6e87a896985b              </t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e700922f-4048-4675-a4ba-d2cc06938661              </t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Hi there. 373 445</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>22990639</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>59175466984</v>
+      </c>
+      <c r="F31" t="n">
+        <v>736</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Undeliverable</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>46220.00752314815</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>46220.0075462963</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>46220.00769675926</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f39dbcee-38a1-42e8-ba37-8c3daeae642b              </t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f899829c-a066-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Twitch es: 9311327</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>22990638</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5566996791600</v>
+      </c>
+      <c r="F32" t="n">
+        <v>724</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>VIVO S.A.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>CLICKSMS</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>46220.00745370371</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>46220.00747685185</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>46220.00769675926</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ec87d2d-29c1-417e-ae99-1015163d65e7              </t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f4ff5628-a066-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AXU-0540
+-11.00847,-55.25015
+AXU-0540 Motorista se moveu.
+</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>22990637</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>59175466984</v>
+      </c>
+      <c r="F33" t="n">
+        <v>736</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>46220.00700231481</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>46220.00702546296</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>46220.0072337963</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fd55652f-1b05-453c-a1eb-f19d82542f66              </t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ddb4d6dc-a066-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Twitch es: 6035776</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>22990636</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>447479994622</v>
+      </c>
+      <c r="F34" t="n">
+        <v>234</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>46220.00653935185</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>46220.00655092593</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>46220.00659722222</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bd0e39f7-4cb1-49ad-ace7-1fa764be0525              </t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f1fa81a6-f77c-4226-be7c-367e83e28579              </t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Hi there. 470 210</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>5 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>22990635</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>447577612456</v>
+      </c>
+      <c r="F35" t="n">
+        <v>234</v>
+      </c>
+      <c r="G35" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>46220.00611111111</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>46220.00613425926</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46220.00619212963</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97f27d11-482a-4b43-9269-4f7754399831              </t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48471cce-c77f-4dad-9bcb-db7246e29610              </t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Hi there. 780 957</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>22990634</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>51935395896</v>
+      </c>
+      <c r="F36" t="n">
+        <v>716</v>
+      </c>
+      <c r="G36" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>46220.00599537037</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>46220.00608796296</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46220.00608796296</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ff543c7-27bc-41e5-b598-900662985bb1              </t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6c9a6418-db35-4c8a-b3f9-05be1b632a3e              </t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 4315
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>8 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>22990633</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>447719194398</v>
+      </c>
+      <c r="F37" t="n">
+        <v>234</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>46220.00516203704</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>46220.00518518518</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46220.00534722222</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32d0ca34-0460-41e1-acb2-5cb08bd54807              </t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93d66604-45f4-46b2-a7d9-e5f4640236ea              </t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Hi there. 344 827</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22990632</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5588994822627</v>
+      </c>
+      <c r="F38" t="n">
+        <v>724</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>46220.005</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>46220.00501157407</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>46220.00520833334</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9dc4277f-f5ce-47cb-b901-e1382a7cced1              </t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76117c9c-a066-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Use o codigo 940098 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>22990631</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>447389165710</v>
+      </c>
+      <c r="F39" t="n">
+        <v>234</v>
+      </c>
+      <c r="G39" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>46220.00453703704</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>46220.00456018518</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>46220.00471064815</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69ee55a7-b437-4f42-9c68-1ba460e8bf0a              </t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31376c18-75c9-4589-a4b1-6454270e0ef9              </t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Hi there. 014 576</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>22990630</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5516982131500</v>
+      </c>
+      <c r="F40" t="n">
+        <v>724</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CUBIC TELECOM BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>AVM</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>46220.00310185185</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>46220.003125</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>46220.00327546296</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e4335da8-a0b9-48b4-9af3-ed362847bfee              </t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14d96d70-a066-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PIN di attivazione: 987398 - Account : jessicarivoiro2020@gmail.com.</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>22990629</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>447572650685</v>
+      </c>
+      <c r="F41" t="n">
+        <v>234</v>
+      </c>
+      <c r="G41" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>46220.00129629629</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>46220.00131944445</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46220.00146990741</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36483aca-7854-40e3-8aa0-1e0ee750940c              </t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">afd05f08-61cf-44b6-b3e9-e1e3b3e6bced              </t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Hi there. 055 153</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,1805 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23001091</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447728705510</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46221.01092592593</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46221.01096064815</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46221.01100694444</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dbab0c82-98f9-4a28-9bd9-5d117f7bec7f              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc864c45-7735-47cf-9779-f22a571e9aed              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 074 295</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23001090</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>447403281197</v>
+      </c>
+      <c r="F3" t="n">
+        <v>234</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46221.0106712963</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46221.01069444444</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46221.01086805556</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9849eda3-7e09-4715-b9eb-aff724ff2b31              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6c6fadf9-c783-40e8-831e-a014c3e49ff4              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Hi there. 664 567</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23001089</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447590822820</v>
+      </c>
+      <c r="F4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46221.00864583333</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46221.00866898148</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46221.00881944445</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ed18aff8-eff0-4add-8653-9f92e3213293              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8398c128-4ee0-4bea-816a-f1d2024ca662              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hi there. 763 457</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23001088</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447986136180</v>
+      </c>
+      <c r="F5" t="n">
+        <v>234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46221.00633101852</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46221.00636574074</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46221.00659722222</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d6ddb17e-6083-4cc2-a8f7-82ab5c1e2e6d              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3e258f7e-096f-46ae-b5dd-808f7151290d              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Hi there. 869 380</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23001087</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5581995012721</v>
+      </c>
+      <c r="F6" t="n">
+        <v>724</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CUBIC TELECOM BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>CLICKSMS</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46221.00585648148</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46221.00587962963</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46221.00604166667</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daa07ad4-6c43-4cb8-acaa-5f9e72cecdda              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd2c173c-a12f-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAT TROVA..
+-3.82729,-32.40796
+CAT TROVA?O EM MOVIMENTO
+</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23001086</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>447440173543</v>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Lycamobile UK Limited</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46221.00559027777</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46221.005625</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46221.0056712963</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">780808ec-07a7-410a-91a7-6a1b30a89c80              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">db0ac408-446b-4d06-aef5-66fecf63088c              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hi there. 638 922</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23001085</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447913405159</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46221.00538194444</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46221.00539351852</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46221.00552083334</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6855840e-6cf9-4923-b6b9-37a6a2c34af0              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1da2efd-9d83-4905-8d91-8077c87f0f96              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 370 547</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23001084</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447478315678</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46221.00450231481</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46221.00452546297</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46221.00467592593</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de3fa669-363b-4e22-9e30-356eb6f75f3d              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8b1126d9-dcf2-49b7-8382-f4fcb4322d3b              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 051 438</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23001083</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>447988321760</v>
+      </c>
+      <c r="F10" t="n">
+        <v>234</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46221.00431712963</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46221.00434027778</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46221.00440972222</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1cba22d2-fb23-4c77-af5b-9bd4bbeeb05c              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">648b4f8a-28ae-4fe0-b584-930e7d869225              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Hi there. 292 049</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>8 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23001082</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>447956172818</v>
+      </c>
+      <c r="F11" t="n">
+        <v>234</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46221.003125</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46221.00314814815</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46221.0033912037</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3985f8fa-2ec2-465c-be6f-9e2d335c1beb              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7a367272-d93f-4b23-b36a-abfef7e030e5              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Hi there. 300 356</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23001081</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447446828323</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46221.00293981482</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46221.00296296296</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46221.00305555556</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ab537c34-a64e-4662-b110-7004f807eece              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">afa673d7-fae4-4de8-8bb9-7321fa31192a              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 299 841</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23001080</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>447590822820</v>
+      </c>
+      <c r="F13" t="n">
+        <v>234</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46221.00239583333</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46221.00241898148</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46221.00261574074</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a889d3f5-f2e6-43ed-8335-32db6f05805f              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0e4df1de-335c-4ae4-8b6f-e3965d35031b              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Hi there. 215 187</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23001079</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>447830348495</v>
+      </c>
+      <c r="F14" t="n">
+        <v>234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46221.00021990741</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46221.00025462963</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46221.00030092592</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536e3488-79ab-44d2-92d6-360153b1368f              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6c261771-d245-4fdd-a10e-2f746cdeecdf              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Hi there. 876 857</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,4423 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23024271</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447914716090</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46222.02702546296</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46222.02704861111</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46222.02712962963</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f2de13d3-707b-440f-b20f-abf7265bd224              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d28a56b7-e962-4e59-8d28-e64e85d33b28              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 926 822</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>9 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23024270</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>56992012259</v>
+      </c>
+      <c r="F3" t="n">
+        <v>730</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Claro Chile sa</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vinacl</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46222.02681712963</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46222.02684027778</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46222.02685185185</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6a9a7141-95a6-4954-bc00-1109d079c924              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d25f65ff-3188-4f86-8944-a4c5c5e16471              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[VINACL] Su retiro ha sido aprobado, por favor espere a que el banco procese la cuenta. Ver progreso VINACL.com</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>3 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23024269</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447474536265</v>
+      </c>
+      <c r="F4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46222.0258912037</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46222.02591435185</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46222.02600694444</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2e5aea3b-164e-4475-a24e-ac2c95baae45              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d8bde3d5-d02d-4fc8-b181-c42e3cd513a9              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hi there. 091 460</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23024268</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5521991403515</v>
+      </c>
+      <c r="F5" t="n">
+        <v>724</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46222.02561342593</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46222.025625</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46222.02572916666</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eeda2917-9def-445a-9b84-a315572428eb              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f079f72c-a1fc-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Use o codigo 592404 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23024267</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5521991403515</v>
+      </c>
+      <c r="F6" t="n">
+        <v>724</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46222.02460648148</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46222.0246412037</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46222.02483796296</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fa1d56dc-88a0-4452-85f4-8eb538638da5              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bd876100-a1fc-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Use o codigo 677717 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23024266</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>447389180606</v>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46222.02319444445</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46222.02321759259</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46222.02340277778</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ef174ce-443a-4099-958c-679aa8b7223e              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9f0a2148-2527-406f-af01-78c9e128bec6              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hi there. 401 097</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23024265</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447767574734</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46222.02199074074</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46222.02200231481</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46222.02228009259</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06450199-b87b-474d-9311-506a223cc495              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287e93a5-9a52-430e-b385-743691453c5d              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 071 027</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>25 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23024264</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>50495652080</v>
+      </c>
+      <c r="F9" t="n">
+        <v>708</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46222.01998842593</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46222.02002314815</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46222.02152777778</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9fdd3b98-1aa0-4e23-a6af-ac56a190db26              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e209523f-5b5f-46eb-8270-ada633bbba59              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Docusign es 840439. Por motivos de seg</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>133</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>133 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23024264</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>50495652080</v>
+      </c>
+      <c r="F10" t="n">
+        <v>708</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46222.01998842593</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46222.02002314815</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46222.02152777778</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26ab6d6b-8656-421d-b280-13e102d9056e              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3b905854-df8c-4078-824b-72dacf09dd3a              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>uridad, no utilices este código fuera de Docusign. No compartas nun</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>133</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>133 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23024264</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>50495652080</v>
+      </c>
+      <c r="F11" t="n">
+        <v>708</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46222.01998842593</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46222.02002314815</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46222.02152777778</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2a436d2a-4d6e-4cc6-9b2a-f62e7f554fe9              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39803127-424d-41ef-b368-2a0f9f35a751              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>ca este código con nadie.</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>133</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>133 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23024263</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>51939857678</v>
+      </c>
+      <c r="F12" t="n">
+        <v>716</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>MOVISTAR(TELEFONICA MOVILES S.A.)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46222.01898148148</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46222.0190625</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46222.01907407407</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84b789aa-8d43-4576-8005-6b92d0fe5fad              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abe6d384-3cb6-4197-a156-e998bbd1b1c7              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 4527
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>8 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23024262</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>85593513246</v>
+      </c>
+      <c r="F13" t="n">
+        <v>456</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46222.01890046296</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46222.01892361111</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46222.01905092593</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22360a8f-0f5f-4a35-96f3-f2e5c0424fa4              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973cfbf8-a1fb-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Your verification code is 360105, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23024261</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>447788990498</v>
+      </c>
+      <c r="F14" t="n">
+        <v>234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46222.01818287037</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46222.01819444444</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46222.01842592593</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a9500e7c-312c-42e5-8c9f-8c45cfe40bad              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b496aedd-6ec1-4449-8508-d3c077ac522d              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Hi there. 104 820</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23024260</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5517991625707</v>
+      </c>
+      <c r="F15" t="n">
+        <v>724</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46222.01626157408</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46222.01628472222</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46222.0165162037</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1b55439e-e9d7-4bd5-b18a-0a37f8ac3b0f              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0f55a9f8-a1fb-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Use o codigo 732280 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23024259</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>447727660136</v>
+      </c>
+      <c r="F16" t="n">
+        <v>234</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46222.01571759259</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46222.01572916667</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46222.01597222222</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">771d5c39-fce2-47cb-9304-197a88d8b7cb              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7d71d7d5-4d42-48ff-a253-729913112760              </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Hi there. 420 944</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23024258</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>447446573826</v>
+      </c>
+      <c r="F17" t="n">
+        <v>234</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46222.01513888889</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46222.01516203704</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46222.01525462963</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811aab71-b780-409e-8954-d9a81592305b              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8430344d-5e34-4b21-ba89-7f772e42c9cf              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Hi there. 311 505</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23024257</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>51931686626</v>
+      </c>
+      <c r="F18" t="n">
+        <v>716</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46222.01076388889</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46222.01082175926</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46222.01083333333</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7fdf3033-4252-4b10-8879-b991d7cde72c              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0036d6e2-c7e9-4b15-9fad-c6f0f2caf414              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>inDrive code: 4242</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23024256</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>447727721457</v>
+      </c>
+      <c r="F19" t="n">
+        <v>234</v>
+      </c>
+      <c r="G19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46222.01056712963</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46222.01059027778</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46222.01064814815</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0fb52a68-38ab-43bf-a994-da17f0198b35              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322f4f2b-4bf0-4867-a8b9-f588f812e31c              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Hi there. 042 121</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23024255</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>447411475634</v>
+      </c>
+      <c r="F20" t="n">
+        <v>234</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46222.00987268519</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46222.00989583333</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46222.01010416666</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9c44fd72-c867-4c6c-869f-138194ac636c              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">082b4e37-7f96-44f9-913f-10f6ea80420c              </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Hi there. 641 451</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23024254</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>447967742982</v>
+      </c>
+      <c r="F21" t="n">
+        <v>234</v>
+      </c>
+      <c r="G21" t="n">
+        <v>33</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46222.00931712963</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46222.00934027778</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46222.00952546296</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25a72fcc-feb8-42db-9e74-ddce85ca2b6f              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b61325fb-e8c6-45b4-9ae6-6272d41a4ac3              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Hi there. 348 361</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23024253</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>59162449291</v>
+      </c>
+      <c r="F22" t="n">
+        <v>736</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46222.00927083333</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46222.00930555556</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46222.00939814815</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226c6dd0-635d-4c81-9c7a-697cb815b62f              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a7d79e5c-a1f9-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 587162</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23024252</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>447411475634</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46222.00850694445</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46222.00853009259</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>46222.00865740741</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84c7a07d-c115-4b15-814a-f3fbb42da759              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d2744176-80ca-4bb9-b45f-840f98b4cb33              </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Hi there. 232 609</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23024251</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>59162449291</v>
+      </c>
+      <c r="F24" t="n">
+        <v>736</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46222.00817129629</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46222.00818287037</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46222.00834490741</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d94af598-36bf-40c2-821d-5870d4dcafc0              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6e8408f4-a1f9-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 102107</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23024250</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>447988334406</v>
+      </c>
+      <c r="F25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46222.00780092592</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46222.00782407408</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46222.00804398148</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4fb3f103-aded-419c-94f4-145bd4701a62              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7fd4ac66-c69d-4deb-9f3d-c7bb58e47a5b              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Hi there. 943 977</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23024249</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>447411475634</v>
+      </c>
+      <c r="F26" t="n">
+        <v>234</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46222.00519675926</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46222.00520833334</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>46222.00527777777</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f8282048-b248-4436-a286-c8370b9cf3ab              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ef3bcf9-cf28-4ee4-8ff8-381c1588ef3b              </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Hi there. 259 567</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23024248</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>447946707307</v>
+      </c>
+      <c r="F27" t="n">
+        <v>234</v>
+      </c>
+      <c r="G27" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46222.00516203704</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46222.00517361111</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46222.00521990741</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2fc6ff36-7225-48cc-b3aa-50bb305bbf19              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aba8fe6c-71a3-4f28-890a-cfc8c5b276f2              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Hi there. 416 740</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>5 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23024247</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>447438772466</v>
+      </c>
+      <c r="F28" t="n">
+        <v>234</v>
+      </c>
+      <c r="G28" t="n">
+        <v>26</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Lycamobile UK Limited</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46222.003125</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46222.00313657407</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46222.00331018519</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81fa5a27-177d-4b9d-8ae5-f65b0ee2da31              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de1dfedb-149b-4460-807d-846848ae940c              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Hi there. 965 533</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23024246</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>447535496473</v>
+      </c>
+      <c r="F29" t="n">
+        <v>234</v>
+      </c>
+      <c r="G29" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>46222.00277777778</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>46222.00277777778</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>46222.00291666666</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7fe61327-1f8f-4199-a831-95b3552db6e4              </t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fd6b0d2c-1691-4663-83e9-7eb49b78d421              </t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Hi there. 099 907</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23024245</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5531985944275</v>
+      </c>
+      <c r="F30" t="n">
+        <v>724</v>
+      </c>
+      <c r="G30" t="n">
+        <v>31</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>OI S.A. (TNL PCS S.A.)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>PRODEGE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>46222.00273148148</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>46222.00274305556</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>46222.00283564815</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5be6b60-51ff-44bd-b7fe-d50b4a1c3034              </t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56171600-a1f8-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Seu codigo e: 890650. Obrigado.</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>9 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>23024244</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>447943067614</v>
+      </c>
+      <c r="F31" t="n">
+        <v>234</v>
+      </c>
+      <c r="G31" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>46222.00252314815</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>46222.00253472223</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>46222.00259259259</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1595ed80-aca7-4b21-b8b6-b030fcb3005b              </t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d3358bc4-102b-45f3-ae8d-16506b948038              </t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Hi there. 274 260</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>23024243</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>447460444042</v>
+      </c>
+      <c r="F32" t="n">
+        <v>234</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>46222.00138888889</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>46222.00140046296</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>46222.00160879629</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b74abc69-2a14-46ab-8f3a-14c0e7d832b1              </t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ceb523a-5053-4686-8433-ffbb517a8c03              </t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Hi there. 965 794</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>23024242</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>447481598811</v>
+      </c>
+      <c r="F33" t="n">
+        <v>234</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>46222.00096064815</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>46222.00100694445</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>46222.00128472222</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cc9a3f63-4076-4792-b2de-f33e2dd7c1b9              </t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e09d2157-e5a7-4578-a15a-f97e64198cdd              </t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Hi there. 777 072</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>28 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,8573 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23040472</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5582994100105</v>
+      </c>
+      <c r="F2" t="n">
+        <v>724</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46223.03971064815</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46223.03973379629</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3d8749f6-a480-47f1-ad2b-b7de0101e859              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f1a3e98c-a2c8-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Use o codigo 578593 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23040471</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>85515458887</v>
+      </c>
+      <c r="F3" t="n">
+        <v>456</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46223.03929398148</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46223.03931712963</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46223.03942129629</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ff6d6fe5-0a34-4346-9e65-b77c43c4e4c2              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc06b8bc-a2c8-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Your verification code is 738896, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23040470</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447473959591</v>
+      </c>
+      <c r="F4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46223.03903935185</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46223.0390625</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46223.03920138889</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d65807d6-5462-4057-b986-b23f6c011f08              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d9b53a09-4ae6-4ffd-8bcf-43ab1ebf2706              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hi there. 945 968</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23040469</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447877725690</v>
+      </c>
+      <c r="F5" t="n">
+        <v>234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46223.03740740741</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46223.03743055555</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46223.03748842593</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1711c85e-d003-4d8f-ab02-fbea5ae14826              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24502c30-dab7-4806-a26f-cd3d6b3ecba6              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Hi there. 618 508</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23040468</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>85598289008</v>
+      </c>
+      <c r="F6" t="n">
+        <v>456</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46223.03511574074</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46223.03515046297</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46223.03527777778</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93eed98d-5d79-4ff5-95b5-7e701e1f95ce              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">057e37c4-a2c8-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Your verification code is 513094, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23040467</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>51929982288</v>
+      </c>
+      <c r="F7" t="n">
+        <v>716</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46223.0340162037</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46223.0340625</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46223.03407407407</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">739cc8ee-c2f6-4b34-8a0c-609fe645a814              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52d34f8a-ebeb-4cda-95b0-7097e10418d2              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>inDrive code: 7288</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>5 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23040466</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>85598289008</v>
+      </c>
+      <c r="F8" t="n">
+        <v>456</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46223.03335648148</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46223.03337962963</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46223.03379629629</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ab6246b-db16-4f65-a066-92b656aa5714              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aa3abf20-a2c7-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Your verification code is 520958, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>38 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23040465</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447770822976</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46223.03309027778</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46223.033125</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46223.03322916666</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309d448e-8bd3-43e9-bf06-b883055771d9              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">637bafbd-74a7-4f64-b094-6fd56637fcc3              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 270 495</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23040464</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>56930085754</v>
+      </c>
+      <c r="F10" t="n">
+        <v>730</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>WOM sa (Novator Partners)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Betazo77</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46223.03305555556</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46223.0330787037</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46223.03309027778</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ff056cfe-dba2-4066-b88c-4abd24018069              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49a6fca5-4354-414c-9846-1d1637fdd09d              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[Betazo77] Su retiro ha sido aprobado, por favor espere a que el banco procese la cuenta. Ver progreso Betazo77.com</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>3 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23040463</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>447481809418</v>
+      </c>
+      <c r="F11" t="n">
+        <v>234</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46223.03255787037</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46223.03256944445</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46223.03273148148</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b2b31862-c24d-4953-8155-f241c536343f              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d1d721e3-03d1-4867-921d-1d7bff6de11b              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Hi there. 779 310</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23040462</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447574394754</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46223.03206018519</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46223.03209490741</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46223.03226851852</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36824051-9fb8-4e12-80e6-fb21ba2acf70              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">384d485e-b680-4e95-95b3-5988bbd4976b              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 623 841</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23040461</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5592991327753</v>
+      </c>
+      <c r="F13" t="n">
+        <v>724</v>
+      </c>
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>VIVO S.A.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>CLICKSMS</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46223.03192129629</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46223.03195601852</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46223.03219907408</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>78</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7abb218c-1856-48e4-806a-f91b986ac8de              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60e92968-a2c7-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARGO8045
+-3.05357,-60.04105
+SPOT Trace has detected that the asset has moved.
+</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>24 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23040460</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>447988179721</v>
+      </c>
+      <c r="F14" t="n">
+        <v>234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46223.03168981482</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46223.03172453704</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46223.03181712963</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fc2b434d-455c-460c-9306-4cdf6ea45989              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f545ef4d-10f6-42ee-8366-43e243929b5c              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Hi there. 130 224</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23040459</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>447930179663</v>
+      </c>
+      <c r="F15" t="n">
+        <v>234</v>
+      </c>
+      <c r="G15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46223.03134259259</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46223.03136574074</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46223.0315625</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54ddf9e3-2928-48ad-b59a-f155aa320f6b              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6b1abd57-0521-471d-8500-b53ca38d6177              </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Hi there. 587 398</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23040458</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>447446191736</v>
+      </c>
+      <c r="F16" t="n">
+        <v>234</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46223.03131944445</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46223.03134259259</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46223.03142361111</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34d91a4c-f653-4bb6-aca9-758490666a07              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e8081d1c-5de1-4bb2-895e-a80576c3fb62              </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Hi there. 679 300</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>9 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23040457</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>51901425611</v>
+      </c>
+      <c r="F17" t="n">
+        <v>716</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46223.03119212963</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46223.03126157408</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46223.03127314815</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84fad159-f7c7-4300-a773-775738828770              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5235d18-c6af-4e6a-a786-205c9770a6b9              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 6480
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23040456</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>447727667694</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46223.03026620371</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46223.0303125</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46223.03038194445</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dab09ee4-ff05-434c-a731-dba0c627a490              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e343d639-eb03-4416-a48f-b62978b2ad7e              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Hi there. 918 198</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23040455</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>447727667694</v>
+      </c>
+      <c r="F19" t="n">
+        <v>234</v>
+      </c>
+      <c r="G19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46223.02940972222</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46223.02943287037</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46223.02962962963</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3beda14b-4679-4278-9925-53fec63dda32              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33ce1b32-da73-4e25-b59f-732f3b0ed6b5              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Hi there. 329 246</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23040454</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>447366240481</v>
+      </c>
+      <c r="F20" t="n">
+        <v>234</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46223.02939814814</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46223.0294212963</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46223.02958333334</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6ab03a9-4e62-4c47-b36d-3bf9dee0f604              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">af4f1315-d41b-4869-ba2d-4492ee8f89dc              </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Hi there. 218 907</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23040453</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>447428861361</v>
+      </c>
+      <c r="F21" t="n">
+        <v>234</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46223.02864583334</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46223.02866898148</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46223.02890046296</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37257ba4-a534-490f-8aca-0927ae5a6119              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2e3955bb-ab27-475b-8a23-96a7776351a6              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Hi there. 954 429</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23040452</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>447432568466</v>
+      </c>
+      <c r="F22" t="n">
+        <v>234</v>
+      </c>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46223.02854166667</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46223.02856481481</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46223.02877314815</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13d0dfef-97b2-465e-86c9-e6be2b5839f1              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38352c1c-1597-40ac-9ada-436254199822              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Hi there. 629 754</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23040451</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>447951562664</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46223.02847222222</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46223.02849537037</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>46223.02855324074</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7875c127-bc37-40ab-96ae-093cb8ff3796              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6a563ebe-d302-4582-8af0-393196b16c0c              </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Hi there. 535 087</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23040450</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>447482910114</v>
+      </c>
+      <c r="F24" t="n">
+        <v>234</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46223.02819444444</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46223.02821759259</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46223.02835648148</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c544a9f3-72da-4ef9-917d-3d1b848e893f              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1df535ae-8120-4f55-b50c-6171da9bce47              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Hi there. 112 251</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23040449</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>447552665200</v>
+      </c>
+      <c r="F25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46223.02767361111</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46223.02770833333</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46223.02777777778</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95486bc6-531c-4450-bcd1-13d941b48936              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45fbf2bc-8ff4-42ad-a209-bb66655c4dfe              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Hi there. 979 904</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>9 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23040448</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>447749377021</v>
+      </c>
+      <c r="F26" t="n">
+        <v>234</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46223.02752314815</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46223.02755787037</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>46223.02777777778</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3782245b-9dcf-493d-9c5f-d346af577c61              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f2e47ddc-7607-4b73-b1f9-b109788cfc03              </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Hi there. 045 346</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23040447</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>51910436336</v>
+      </c>
+      <c r="F27" t="n">
+        <v>716</v>
+      </c>
+      <c r="G27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46223.02690972222</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46223.02694444444</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46223.02695601852</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8343d7ad-8f8e-4c95-a6d9-a6674efcb9b8              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70f00a96-ff06-4e71-935f-9e94ced0029a              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 4522
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>4 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23040446</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>447967827295</v>
+      </c>
+      <c r="F28" t="n">
+        <v>234</v>
+      </c>
+      <c r="G28" t="n">
+        <v>33</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46223.02643518519</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46223.02645833333</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46223.02667824074</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03d9d176-95e4-4a62-bfbb-7e78c4775591              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1d225e4e-7c30-4a4a-941a-19488a14b058              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Hi there. 380 295</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23040445</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>447988179721</v>
+      </c>
+      <c r="F29" t="n">
+        <v>234</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>46223.02623842593</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>46223.02626157407</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>46223.02631944444</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42ac5b42-af2d-423f-a6fc-766b1deab6da              </t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3303221a-3fcb-45a6-ac4b-f31f57d9653a              </t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Hi there. 508 482</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23040444</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>51931315671</v>
+      </c>
+      <c r="F30" t="n">
+        <v>716</v>
+      </c>
+      <c r="G30" t="n">
+        <v>15</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>46223.02600694444</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>46223.02607638889</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>46223.02607638889</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85081247-0e18-43ac-99ea-2131cccdc4af              </t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6badd79c-00da-46a2-a6cd-f27ea5d2ad90              </t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>inDrive code: 1445</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>23040443</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>447552665200</v>
+      </c>
+      <c r="F31" t="n">
+        <v>234</v>
+      </c>
+      <c r="G31" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>46223.02539351852</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>46223.02541666666</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>46223.02561342593</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e3422ff1-356a-4b84-b5ce-d961941e92f5              </t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f12a582d-478c-45ca-bf7d-fe32a42e3f02              </t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Hi there. 655 541</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>23040442</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>447731174689</v>
+      </c>
+      <c r="F32" t="n">
+        <v>234</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>46223.02327546296</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>46223.02328703704</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>46223.02347222222</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1c1aec4c-f61a-4b2e-b980-3a2e125e688e              </t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c348e1ae-14e3-49ff-901c-e7ec0d1f1f95              </t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Hi there. 168 526</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>23040441</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5567981362909</v>
+      </c>
+      <c r="F33" t="n">
+        <v>724</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CUBIC TELECOM BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>46223.02277777778</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>46223.02280092592</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>46223.02296296296</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05df0fe9-b69b-42f5-bfd2-7d8eabab07fd              </t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898cd0b4-a2c5-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>ÄTikTokÑ 5758 e seu codigo de verificacao</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>23040440</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>447475178259</v>
+      </c>
+      <c r="F34" t="n">
+        <v>234</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>46223.0225462963</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>46223.02255787037</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>46223.02270833333</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d885cc4f-5b31-406a-9617-a8f9674ccbe9              </t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247e0d8e-1a6b-4b7d-a227-7e57f48e2247              </t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Hi there. 258 458</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>23040439</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>447388049722</v>
+      </c>
+      <c r="F35" t="n">
+        <v>234</v>
+      </c>
+      <c r="G35" t="n">
+        <v>15</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>46223.02245370371</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>46223.02247685185</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46223.02271990741</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f1f50a4f-4818-41ac-a012-458aa7d72f61              </t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4667898c-c394-4955-a7da-b3c90fe84c0a              </t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Hi there. 472 180</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>23040438</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>447475178259</v>
+      </c>
+      <c r="F36" t="n">
+        <v>234</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>46223.02155092593</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>46223.0215625</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9374ddbe-780f-4b05-a8e9-18c7caf0cea3              </t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc45402b-5374-417f-b902-0d5ba55c3db0              </t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Hi there. 259 332</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>23040437</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>447445450091</v>
+      </c>
+      <c r="F37" t="n">
+        <v>234</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>46223.02143518518</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>46223.02146990741</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46223.02151620371</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1bf5d0ef-6bff-4bcd-94e0-20e21615b53e              </t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e93e9e06-fc7d-40b3-a793-3bea1c4b49b6              </t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Hi there. 760 396</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>23040436</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>447378129854</v>
+      </c>
+      <c r="F38" t="n">
+        <v>234</v>
+      </c>
+      <c r="G38" t="n">
+        <v>20</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>46223.02084490741</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>46223.02086805556</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>46223.02108796296</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">469674bc-98e5-477f-880b-fe61183d9787              </t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b9d23413-4d03-4a74-b3b4-4b1c4da3a38e              </t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Hi there. 897 137</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>23040435</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5511991109783</v>
+      </c>
+      <c r="F39" t="n">
+        <v>724</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>46223.02046296297</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>46223.02048611111</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>46223.02068287037</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0c51fa7e-4ee4-465d-b91f-f19a33d2be1f              </t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272397c-a2c5-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Seu codigo de verificacao da Choice Hotels: 308044. Nao compartilhe.</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>23040434</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>447846328077</v>
+      </c>
+      <c r="F40" t="n">
+        <v>234</v>
+      </c>
+      <c r="G40" t="n">
+        <v>20</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>46223.02016203704</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>46223.02018518518</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>46223.0203587963</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64b123e9-bd9f-4005-a3fd-acd2897a2419              </t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0f0cdd0c-b246-4d3d-902c-fe612c60b637              </t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Hi there. 642 321</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>23040433</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>447447691173</v>
+      </c>
+      <c r="F41" t="n">
+        <v>234</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>46223.01903935185</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>46223.01905092593</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46223.01912037037</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b78b9cb8-593f-4bfb-8e4f-aab7243a679e              </t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600cedcf-4f05-4b5b-97f2-3b7ade1520e7              </t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Hi there. 948 952</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>23040432</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>447846328077</v>
+      </c>
+      <c r="F42" t="n">
+        <v>234</v>
+      </c>
+      <c r="G42" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>46223.01890046296</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>46223.01891203703</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>46223.01905092593</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b37bb5a5-fe31-494d-a455-9dc1134d0d42              </t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c8dec974-63c2-48eb-bea7-22d730ba4387              </t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Hi there. 783 175</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>23040431</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>447756417459</v>
+      </c>
+      <c r="F43" t="n">
+        <v>234</v>
+      </c>
+      <c r="G43" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>46223.01888888889</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>46223.01890046296</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>46223.01902777778</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">613d500e-e878-449a-a122-5b321ee3b897              </t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ce468aa-ea16-4e6a-b801-2ec1214d95d2              </t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Hi there. 633 558</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>23040430</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5521993280071</v>
+      </c>
+      <c r="F44" t="n">
+        <v>724</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>PRODEGE</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>46223.01811342593</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>46223.018125</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>46223.01849537037</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2dda2a90-4704-4d90-a7dd-b6235457db05              </t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98e40644-a2c4-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Your code is: 6623. Thank you.</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>33</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>33 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>23040429</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>56991384812</v>
+      </c>
+      <c r="F45" t="n">
+        <v>730</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Entel PCS Telecomunicaciones sa</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>coquimbocl</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>46223.01777777778</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>46223.01783564815</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>46223.01784722223</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>119</v>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08b25785-ac33-43e6-a2ee-39e3127cc335              </t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7c9e9418-fc0a-4114-b3cb-2796b3e01fe5              </t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[COQUIMBOCL] Su retiro ha sido aprobado, por favor espere a que el banco procese la cuenta. Ver progreso COQUIMBOCL.com</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>23040428</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>447366635005</v>
+      </c>
+      <c r="F46" t="n">
+        <v>234</v>
+      </c>
+      <c r="G46" t="n">
+        <v>20</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>46223.01696759259</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>46223.01699074074</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>46223.01728009259</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06d529bf-d534-4849-83ac-9abc681af174              </t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a6101098-774a-4037-aeba-f03d65c218a9              </t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Hi there. 081 814</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>27 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>23040427</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>447492058847</v>
+      </c>
+      <c r="F47" t="n">
+        <v>234</v>
+      </c>
+      <c r="G47" t="n">
+        <v>20</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>46223.016875</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>46223.01690972222</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>46223.01709490741</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13f74b2b-e582-4268-a56f-55ef7322d16b              </t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">713c5121-1130-402b-ae98-bf87de6abc7b              </t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Hi there. 933 024</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>23040426</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>447362436777</v>
+      </c>
+      <c r="F48" t="n">
+        <v>234</v>
+      </c>
+      <c r="G48" t="n">
+        <v>20</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>46223.01635416667</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>46223.01637731482</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>46223.01648148148</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c711584c-f84a-489f-b6e1-2b134909da38              </t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abd6be76-6e29-468c-aca7-6328dce19be6              </t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Hi there. 788 524</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>23040425</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>59176693384</v>
+      </c>
+      <c r="F49" t="n">
+        <v>736</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>AIRBNB</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>46223.01252314815</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>46223.0125462963</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>46223.01266203704</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e5ff91c3-5b95-4a63-8bee-c02539725bf7              </t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7926ddd4-a2c3-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Airbnb es 5419.</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>23040424</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5551999172559</v>
+      </c>
+      <c r="F50" t="n">
+        <v>724</v>
+      </c>
+      <c r="G50" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>VIVO S.A.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>CLICKSMS</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>46223.01208333333</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>46223.01210648148</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>46223.01228009259</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a434eaa-d01b-4197-a5ed-6c4a69732db7              </t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62f311e8-a2c3-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>SpotRotas
+ll=-32.62587,-60.16663 
+ SPOT Movement Alert:Entramos em movimento!</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>23040423</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>447943322617</v>
+      </c>
+      <c r="F51" t="n">
+        <v>234</v>
+      </c>
+      <c r="G51" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>46223.01083333333</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>46223.01084490741</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>46223.01106481482</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45069551-a957-473a-b68b-4518e55c01c2              </t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">482a6ce2-8ac7-4061-9bac-77c607104108              </t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Hi there. 197 024</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>23040422</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>59176627939</v>
+      </c>
+      <c r="F52" t="n">
+        <v>736</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>46223.01060185185</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>46223.010625</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>46223.01083333333</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36484085-58bc-4aa6-ae82-8a8d11361a65              </t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162629e8-a2c3-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Twitch es: 151626</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>23040421</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>447450069691</v>
+      </c>
+      <c r="F53" t="n">
+        <v>234</v>
+      </c>
+      <c r="G53" t="n">
+        <v>20</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>46223.01053240741</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>46223.01056712963</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>46223.010625</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426b70e7-eaf2-4fab-af17-92efbadbbaac              </t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ff149983-6b5f-4722-860f-39039c78b68a              </t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>Hi there. 675 438</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>8 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>23040420</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>447877433001</v>
+      </c>
+      <c r="F54" t="n">
+        <v>234</v>
+      </c>
+      <c r="G54" t="n">
+        <v>20</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>46223.01017361111</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>46223.01020833333</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>46223.01042824074</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b7eb4114-2f56-4c5a-9fd6-3ca54a6339b7              </t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e25da886-fac4-4467-a60e-3d653a689165              </t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Hi there. 728 080</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>23040419</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>447894562807</v>
+      </c>
+      <c r="F55" t="n">
+        <v>234</v>
+      </c>
+      <c r="G55" t="n">
+        <v>10</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>46223.00965277778</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>46223.0096875</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>46223.00997685185</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">756afa08-f7c5-4f5b-badf-803d0d7fe8d9              </t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78e7884a-843d-430d-b01b-ee9f9fd453dd              </t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Hi there. 729 055</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>28 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>23040418</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5514988033942</v>
+      </c>
+      <c r="F56" t="n">
+        <v>724</v>
+      </c>
+      <c r="G56" t="n">
+        <v>31</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>OI S.A. (TNL PCS S.A.)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>46223.0096412037</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>46223.00966435186</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>46223.01008101852</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91bf9690-aae2-4ceb-a5ec-b1f2e3f7857a              </t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e53d98b8-a2c2-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Use o codigo 016405 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>38 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>23040417</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>447576628413</v>
+      </c>
+      <c r="F57" t="n">
+        <v>234</v>
+      </c>
+      <c r="G57" t="n">
+        <v>20</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>46223.00946759259</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>46223.00949074074</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>46223.00973379629</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37b69e9e-dbe7-4e04-b669-9f881deafd4d              </t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2250a670-7462-40eb-8cba-fb688838de9f              </t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Hi there. 523 916</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>23040416</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5549988032002</v>
+      </c>
+      <c r="F58" t="n">
+        <v>724</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>myCicero</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>46223.00929398148</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>46223.00931712963</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>46223.00945601852</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a35f2f17-bab6-4ecf-92bd-88175281aa53              </t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d336d3f8-a2c2-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Activation PIN: 544554 - Account : arlindoneuro@gmail.com.
+ @ #544554</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>23040415</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>447590822820</v>
+      </c>
+      <c r="F59" t="n">
+        <v>234</v>
+      </c>
+      <c r="G59" t="n">
+        <v>10</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>46223.00613425926</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>46223.00615740741</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>46223.00638888889</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4b89e501-0ad6-401f-9c2f-086e22403613              </t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3acf2dad-b77f-4abd-8f2d-b90e32e46d2b              </t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Hi there. 057 557</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>23040414</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>447590822820</v>
+      </c>
+      <c r="F60" t="n">
+        <v>234</v>
+      </c>
+      <c r="G60" t="n">
+        <v>10</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>46223.00453703704</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>46223.00456018518</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>46223.00469907407</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a165e6ba-1a0e-4c47-938e-dce1437920a1              </t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62353079-d5e0-4375-904c-ee32ce7e72fb              </t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Hi there. 547 536</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>23040413</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5514988033942</v>
+      </c>
+      <c r="F61" t="n">
+        <v>724</v>
+      </c>
+      <c r="G61" t="n">
+        <v>31</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>OI S.A. (TNL PCS S.A.)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>46223.0033912037</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>46223.00341435185</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>46223.00354166667</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a9869a75-e4f6-4e77-b326-6da08863cc40              </t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a319cb74-a2c1-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Use o seu codigo unico do eneba.com: 467601</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>23040412</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>51916097764</v>
+      </c>
+      <c r="F62" t="n">
+        <v>716</v>
+      </c>
+      <c r="G62" t="n">
+        <v>15</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>46223.00332175926</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>46223.00335648148</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>46223.00336805556</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456d5c27-5dbb-4c8e-a2b9-018b173fe1f7              </t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22b26180-97b1-4ed2-8de6-5583bb77da3c              </t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>inDrive code: 5493</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>4 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>23040411</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>51928777061</v>
+      </c>
+      <c r="F63" t="n">
+        <v>716</v>
+      </c>
+      <c r="G63" t="n">
+        <v>15</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>46223.00134259259</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>46223.00136574074</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>46223.00137731482</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47c67484-f00d-4fc9-9e37-fce5b2592b7e              </t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9fb3e9fd-4da9-472e-b360-a4106cd7d093              </t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 1445
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>3 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,3736 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23055414</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447842791413</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46224.02636574074</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46224.02638888889</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46224.02653935185</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8d323785-62df-4398-b71f-b53e7ed6f579              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ae7913e-3b8d-4c1e-8382-82ed21274dcc              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 181 343</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23055413</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>447512499253</v>
+      </c>
+      <c r="F3" t="n">
+        <v>234</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46224.02450231482</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46224.02453703704</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46224.0246875</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824cbe5f-8071-4207-aa9d-0061441eb432              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e20cf31-b7f9-44fb-ac22-73971b35e324              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Hi there. 048 449</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23055412</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5531989706487</v>
+      </c>
+      <c r="F4" t="n">
+        <v>724</v>
+      </c>
+      <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OI S.A. (TNL PCS S.A.)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46224.0234375</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46224.02346064815</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46224.02355324074</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">068b3877-0472-4390-bc7b-43817bc2d116              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d6063948-a38e-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Use o codigo 088677 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23055411</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447576977131</v>
+      </c>
+      <c r="F5" t="n">
+        <v>234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46224.02327546296</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46224.02331018518</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46224.02346064815</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97408ab9-6fda-4008-9dde-eb36bfc783d7              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0c1232c8-ae6f-4da5-a080-8cc0938a4389              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Hi there. 266 005</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23055410</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>447367900063</v>
+      </c>
+      <c r="F6" t="n">
+        <v>234</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46224.02116898148</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46224.02119212963</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46224.02135416667</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3da5b5fd-264a-44f9-aa8c-d165e3836b89              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7b3eed34-a7af-4674-aa42-d05febdef8fa              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Hi there. 039 198</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23055409</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>447367900063</v>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46224.01994212963</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46224.01996527778</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46224.02013888889</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8f350d38-37d9-4fd1-9df0-67fd31ec8742              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aec06fed-38f6-4324-a899-d3a2fe48edce              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hi there. 360 123</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23055408</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447547876715</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46224.01966435185</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46224.01971064815</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46224.01987268519</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc7336f6-1223-4951-9658-5e406644a8fb              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ef304fc-e63b-4383-b2f5-37134e0a181f              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 595 185</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23055407</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447900044030</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46224.01704861111</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46224.01707175926</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46224.01723379629</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150c31e5-8084-4360-b20d-39119d18b2f6              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e0ffa63c-9586-4f25-9331-19a028ef2c0e              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 107 008</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23055406</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>447474317804</v>
+      </c>
+      <c r="F10" t="n">
+        <v>234</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46224.01586805555</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46224.01587962963</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46224.01606481482</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd0da8dc-98dc-4b17-93f3-9d388cdc2365              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10b1ee36-3a87-4985-b6c0-c3ad703d3ba6              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Hi there. 305 996</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23055405</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>447863132365</v>
+      </c>
+      <c r="F11" t="n">
+        <v>234</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46224.01486111111</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46224.01488425926</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46224.01505787037</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7a2fe325-68d2-4e58-8122-190c70d79647              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0ad2ed70-9277-4924-aacc-57d6d53fe7c8              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Hi there. 362 764</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23055404</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447964330340</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46224.0141087963</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46224.01416666667</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46224.01431712963</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d8bf5987-35b6-42b1-b64f-c593b92040c6              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e3a04ace-15d9-45e3-8f08-dd0e3f165056              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 353 067</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23055403</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>447426231063</v>
+      </c>
+      <c r="F13" t="n">
+        <v>234</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46224.0134375</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46224.01346064815</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46224.01364583334</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5dd2f923-79b2-4098-b37f-13a1a667b0dc              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f4f5bc33-af5b-4c7e-89c1-2db8adaff060              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Hi there. 185 352</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23055402</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>85593887721</v>
+      </c>
+      <c r="F14" t="n">
+        <v>456</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46224.01153935185</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46224.0115625</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46224.01170138889</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e1f37f2-ea30-428c-908a-66c75b0be61a              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7132d8ac-a38c-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Your verification code is 603402, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23055401</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>447412907063</v>
+      </c>
+      <c r="F15" t="n">
+        <v>234</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46224.01121527778</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46224.01122685185</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46224.01140046296</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">962ca2c7-152f-47a0-800c-2470a3267be4              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2c5a3916-f508-43d2-8eab-344d10d3fad1              </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Hi there. 162 538</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23055400</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>447487500720</v>
+      </c>
+      <c r="F16" t="n">
+        <v>234</v>
+      </c>
+      <c r="G16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46224.01047453703</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46224.01049768519</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46224.0106712963</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc848095-fad7-4e3e-bff6-c87ed4a5ea33              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f0f32664-cbca-41e1-ace0-dbb2d1ed9e01              </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Hi there. 332 811</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23055399</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>447412907063</v>
+      </c>
+      <c r="F17" t="n">
+        <v>234</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46224.00947916666</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46224.00953703704</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46224.00971064815</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93d1bd20-122b-43b4-9101-e6daec54ecbe              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20df0d99-0348-43fb-8a63-fe478453308f              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Hi there. 435 751</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23055398</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>447947940289</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46224.00853009259</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46224.00855324074</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46224.00872685185</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37fe827d-48fb-4de3-83d9-ea0b81ad42e6              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666fa276-c610-4620-b473-a76dd2c8b27b              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Hi there. 493 364</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23055397</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>51901654737</v>
+      </c>
+      <c r="F19" t="n">
+        <v>716</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46224.00846064815</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46224.00849537037</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46224.00849537037</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74a5c2bd-0741-45e9-ace0-7d9bcbbc4bab              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34dbe36e-1925-4af9-975b-16322224ad39              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 7616
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>3 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23055396</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>447446493862</v>
+      </c>
+      <c r="F20" t="n">
+        <v>234</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46224.00690972222</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46224.00693287037</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46224.00709490741</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49e44523-55f2-42c3-a6bd-3a2abb22aaa9              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6cceac62-024f-40a9-aae6-45dba079d3b5              </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Hi there. 846 589</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23055395</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>447825086867</v>
+      </c>
+      <c r="F21" t="n">
+        <v>234</v>
+      </c>
+      <c r="G21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46224.00585648148</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46224.00587962963</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46224.00606481481</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">972dbdf3-932e-48f2-b2a1-1bf549d0bf5a              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5c35ebe2-6ff5-459a-b721-9008775e885f              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Hi there. 544 148</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23055394</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>51935395508</v>
+      </c>
+      <c r="F22" t="n">
+        <v>716</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46224.00546296296</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46224.00549768518</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46224.00549768518</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9fb5bed4-af94-423c-865e-81ca13c6b94e              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6fc98aab-cce7-404e-8d17-c8ed8de250d0              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 1432
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>3 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23055393</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>447828008668</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46224.00472222222</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46224.00474537037</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>46224.00489583334</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d4cdf885-43f7-46ae-80fc-e6b40c32a072              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c298ef7d-4bb7-4bcf-ada7-74c8c2ccb8e7              </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Hi there. 654 915</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23055392</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>85569307647</v>
+      </c>
+      <c r="F24" t="n">
+        <v>456</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46224.00335648148</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46224.00337962963</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46224.00347222222</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9d3389fa-5d06-4d7e-a617-76716681827c              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cbc14e5c-a38a-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Your verification code is 372568, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23055391</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>447846193054</v>
+      </c>
+      <c r="F25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46224.0025</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46224.00251157407</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46224.00268518519</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5062680-b228-46cd-a5a0-445eb9c89071              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3217fb4c-377c-46f0-b949-7c846c16f136              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Hi there. 063 594</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23055390</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>447459416444</v>
+      </c>
+      <c r="F26" t="n">
+        <v>234</v>
+      </c>
+      <c r="G26" t="n">
+        <v>26</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Lycamobile UK Limited</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46224.00105324074</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46224.00106481482</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>46224.00122685185</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53eac0e6-064e-4df7-9234-b5c42a8c996b              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b88d704f-c3b0-45b1-adc7-c0d183f3207c              </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Hi there. 103 564</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23055389</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>59162705095</v>
+      </c>
+      <c r="F27" t="n">
+        <v>736</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46224.00100694445</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46224.00101851852</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46224.00107638889</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>87</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">db46ed13-3936-41d1-8b9a-e677f233f68e              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">522ca1a4-a38a-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; Codigo de WhatsApp Business: 266-025
+No compartas este codigo con nadie
+rJbA/XP1K+V</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23055388</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>59177774964</v>
+      </c>
+      <c r="F28" t="n">
+        <v>736</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>AIRBNB</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46224.00049768519</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46224.00052083333</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46224.00068287037</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29784d2d-aa3f-450f-9407-c8fa232ab1d1              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38662c04-a38a-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Tu código de verificación para Airbnb es 2172.</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,6594 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23120006</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447452902976</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46225.02760416667</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46225.02762731481</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b9c95c4a-bf0c-4416-851f-23d94cb197f9              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ca572b47-a2e0-464d-88b9-10472fa7a49d              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 651 371</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23120005</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>85581825474</v>
+      </c>
+      <c r="F3" t="n">
+        <v>456</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46225.0265162037</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46225.02652777778</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46225.02666666666</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e612dc80-40b9-4d99-a273-c87509d929ad              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9e666040-a458-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Your verification code is 9223, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23120004</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447380525390</v>
+      </c>
+      <c r="F4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46225.02604166666</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46225.02605324074</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46225.0262037037</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ad4d7ac-db99-468c-97e0-a50e7928b2d3              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97042313-1f30-440b-980a-f9abf7e19c1e              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hi there. 406 874</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23120003</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447788421673</v>
+      </c>
+      <c r="F5" t="n">
+        <v>234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46225.02590277778</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46225.02592592593</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46225.02606481482</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c85a0f67-652c-479b-a674-a5a259f038ee              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">841aba75-7181-4c25-b92b-6e64f3c901d6              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Hi there. 651 272</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23120002</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>51917816788</v>
+      </c>
+      <c r="F6" t="n">
+        <v>716</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46225.0258912037</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46225.02596064815</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46225.02596064815</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9a3ac385-e119-4c6d-9731-1d579c0f5460              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61253d25-7228-4512-b3a8-41d0d943b38b              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 8552
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23120001</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>447877731138</v>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46225.02520833333</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46225.02521990741</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46225.02538194445</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ee14321d-536c-4ae3-9485-7c68e6372120              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feb89584-3891-43ac-aac5-4837c5eb33ba              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hi there. 067 169</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23120000</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447570660622</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46225.02494212963</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46225.02496527778</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46225.02509259259</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11a4e9e8-f871-41bd-8c97-e7b1aa5e4b2e              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ee562bae-ad4d-405c-b403-f0a648c16429              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 684 041</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23119999</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447537852457</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46225.02400462963</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46225.02402777778</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46225.02414351852</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5267676e-17a9-4580-b92b-adddeb60b6c3              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d55e95a0-3071-429e-a275-b46fc7036d46              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 149 656</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23119998</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>85570708404</v>
+      </c>
+      <c r="F10" t="n">
+        <v>456</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46225.02342592592</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46225.02344907408</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46225.02354166667</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6bf4fd04-c883-4b90-a0ee-b08eef78a199              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ffcd3b84-a457-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Your verification code is 0389, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23119997</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5544984643431</v>
+      </c>
+      <c r="F11" t="n">
+        <v>724</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>OI MOVEL S.A. - (BRASILTELECOM)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Ding</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46225.02306712963</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46225.02310185185</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46225.02327546296</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">441e9b7b-60a4-4251-a7c7-93fb61550d6d              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ed846a7c-a457-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>934269 e seu codigo para Suno.</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23119996</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447532780799</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46225.02209490741</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46225.02210648148</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46225.02238425926</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a747aeaf-a1d1-4a04-abc6-6db51dd35603              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b0b0c315-4570-45d8-93f6-4cac18fa5e82              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 116 461</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>25 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23119995</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59162184919</v>
+      </c>
+      <c r="F13" t="n">
+        <v>736</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>TINDER</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46225.02203703704</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46225.02204861111</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46225.02214120371</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46a8e073-c30b-4d98-b6be-7fd67c19a107              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b7a97bf8-a457-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; Tu codigo de Tinder es 047122 dwEzWOx6XSV</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>9 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23119994</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>85510960389</v>
+      </c>
+      <c r="F14" t="n">
+        <v>456</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46225.02196759259</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46225.02199074074</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46225.02209490741</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6da36594-9d78-4cb8-86ba-a1045b0d5711              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4a91c68-a457-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Your verification code is 4327, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23119993</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>56993041506</v>
+      </c>
+      <c r="F15" t="n">
+        <v>730</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Entel PCS Telecomunicaciones sa</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Betazo77</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46225.02194444444</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46225.02196759259</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46225.02199074074</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e33acb8e-085b-47e5-9d4c-d39fafbd2165              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ee2fd64-f265-421b-a909-e94539b6023c              </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[Betazo77] Su retiro ha sido aprobado, por favor espere a que el banco procese la cuenta. Ver progreso Betazo77.com</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>4 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23119992</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>56949822555</v>
+      </c>
+      <c r="F16" t="n">
+        <v>730</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>WOM sa (Novator Partners)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Betazo77</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46225.02194444444</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46225.02196759259</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46225.02199074074</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37877f0d-ad9f-4d36-b5f2-67a293416e3b              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52c13937-482b-4e61-b6f4-465fa0dc85db              </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[Betazo77] Su retiro ha sido aprobado, por favor espere a que el banco procese la cuenta. Ver progreso Betazo77.com</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>4 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23119991</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>447506279600</v>
+      </c>
+      <c r="F17" t="n">
+        <v>234</v>
+      </c>
+      <c r="G17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46225.02148148148</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46225.02150462963</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46225.0216087963</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ea4429c-9658-442e-8a57-b1ca326677f4              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600bd085-1651-4358-908b-d06dd3053f59              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Hi there. 917 069</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23119990</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>447968250699</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>33</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46225.02107638889</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46225.02109953704</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46225.02128472222</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8d1da21b-f4e4-4346-be84-75bb79407027              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59c26125-63ed-499c-a5b0-b1738fb6d1a2              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Hi there. 289 413</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23119989</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59178480961</v>
+      </c>
+      <c r="F19" t="n">
+        <v>736</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46225.02079861111</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46225.02081018518</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46225.0209375</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d18958fe-77f3-48df-8c3c-0a38ad80a3a1              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77761c6c-a457-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Twitch es: 836210</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23119988</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>447548355722</v>
+      </c>
+      <c r="F20" t="n">
+        <v>234</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46225.02015046297</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46225.02017361111</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46225.02039351852</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e6266fa6-49b0-4bfa-a772-9259f956b434              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">713bd399-c99e-439b-96b3-77c1d51d967f              </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Hi there. 196 170</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23119987</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>447452989337</v>
+      </c>
+      <c r="F21" t="n">
+        <v>234</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46225.01983796297</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46225.01986111111</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46225.01997685185</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e6b64998-d0f9-4eb6-8fa2-6bef94c88f32              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9a2ff987-44fb-4071-ae52-3974d9679716              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Hi there. 433 194</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23119986</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>447728352212</v>
+      </c>
+      <c r="F22" t="n">
+        <v>234</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46225.01802083333</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46225.01803240741</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46225.01817129629</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5abaf55d-bb7e-4e28-98b7-443f45883d8a              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147ab88e-beb8-4ff5-a321-9f887c7aa881              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Hi there. 700 757</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23119985</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>447728352212</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46225.01784722223</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46225.01787037037</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>46225.01797453704</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1a7894fa-8acf-41b7-a051-7a27f1775fa7              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">417afbb9-d796-48e5-a810-d21d1cfda62a              </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Hi there. 547 967</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23119984</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>85586904777</v>
+      </c>
+      <c r="F24" t="n">
+        <v>456</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46225.01765046296</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46225.01765046296</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46225.01773148148</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fe2b8575-7c1b-4d9e-9f70-e35b2c06be7f              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d53fb0f8-a456-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Your verification code is 9001, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23119983</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>447532780799</v>
+      </c>
+      <c r="F25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46225.01725694445</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46225.01728009259</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46225.01748842592</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aafb50a4-8db7-4347-bffb-61e9b7a04d85              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74dc227e-9f89-46df-abe2-3b3c630807fa              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Hi there. 998 036</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23119982</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>85569950376</v>
+      </c>
+      <c r="F26" t="n">
+        <v>456</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46225.01516203704</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46225.01518518518</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>46225.01554398148</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6790184d-06e3-4dcb-8f3b-db1056b1cbeb              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5652381c-a456-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Your verification code is 1476, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>33</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>33 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23119981</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>447449446147</v>
+      </c>
+      <c r="F27" t="n">
+        <v>234</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46225.0147337963</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46225.01474537037</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46225.01488425926</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c77e0ad1-dcb0-4022-8f1f-5b8ed0637c28              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122c2c30-0a08-44cf-ae3d-e76a2c08129b              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Hi there. 400 007</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23119980</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>447447154660</v>
+      </c>
+      <c r="F28" t="n">
+        <v>234</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46225.01393518518</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46225.01398148148</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46225.01420138889</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06741851-7c8b-4f07-86e1-b8ec8fa62b49              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14bba519-bc21-40f6-9b44-494e13b8163a              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Hi there. 348 184</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23119979</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>56928963940</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MCC/MNC Not Found</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>YODJWN</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>46225.01385416667</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>46225.01387731481</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>129</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>1007</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9141bae2-15e9-4eb0-9179-aebb71ae5479              </t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Tu retiro en Melb£t no se proceso. Solo escribe al chat de soporte y resolveremos el problema sin demoras https://meb.ink/mh34AhQ</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23119978</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>85597914312</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MCC/MNC Not Found</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>46225.01336805556</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>46225.01336805556</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>1007</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f96a0275-8898-4e4d-b5df-c75e53f5b8ac              </t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Your verification code is 1856, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>23119977</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>40743621590</v>
+      </c>
+      <c r="F31" t="n">
+        <v>226</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Orange Romania</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>AOL</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>46225.01324074074</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>46225.01326388889</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>46225.01328703704</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>99</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">671cdb71-6e63-4bf8-8898-949c16543c59              </t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ab1932d1-a047-4227-ae61-e75f1d104452              </t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>AOL: Your verification code is 079935. We'll NEVER call or text you for this code. DO NOT share it.</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>4 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>23119976</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>40743621590</v>
+      </c>
+      <c r="F32" t="n">
+        <v>226</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Orange Romania</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>AOL</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>46225.01087962963</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>46225.01090277778</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>46225.01092592593</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>99</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60906ee9-04e2-4b6e-a9c7-99c0aca91299              </t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0864661b-9091-470d-b039-08224da6b698              </t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>AOL: Your verification code is 531477. We'll NEVER call or text you for this code. DO NOT share it.</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>4 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>23119975</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>447515165656</v>
+      </c>
+      <c r="F33" t="n">
+        <v>234</v>
+      </c>
+      <c r="G33" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>46225.010625</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>46225.01064814815</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>46225.01085648148</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740de5ba-c79f-4d41-9edc-b41ef50ba52d              </t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b8df1c97-1d1c-4c3a-ab2e-ccb32d7be50e              </t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Hi there. 743 266</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>23119974</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>447515025445</v>
+      </c>
+      <c r="F34" t="n">
+        <v>234</v>
+      </c>
+      <c r="G34" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>46225.01054398148</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>46225.01056712963</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>46225.01085648148</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16579e6b-0f15-4bd4-9583-c17014a4a430              </t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ce0f4974-83d0-4f58-b8d7-05176f424b8e              </t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Hi there. 518 171</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>27 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>23119973</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>85516394157</v>
+      </c>
+      <c r="F35" t="n">
+        <v>456</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>46225.00956018519</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>46225.00957175926</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46225.00967592592</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8a43f4c5-0e3b-46ef-aba7-92f5a5bca192              </t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35117f1c-a455-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Your verification code is 2509, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>23119972</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>447515165656</v>
+      </c>
+      <c r="F36" t="n">
+        <v>234</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>46225.00909722222</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>46225.00912037037</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46225.00934027778</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60c1876d-66ed-447e-a592-7702f29d5252              </t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bec3491e-3613-46a3-b059-f78be8c491a9              </t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Hi there. 886 776</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>23119971</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>447474141709</v>
+      </c>
+      <c r="F37" t="n">
+        <v>234</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>46225.00825231482</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>46225.00827546296</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46225.00854166667</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">983d0042-7760-4e04-9ca6-fd66d50655f0              </t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6016976-de24-4798-9667-ef3238968bff              </t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Hi there. 877 960</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>25 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>23119970</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>50492463599</v>
+      </c>
+      <c r="F38" t="n">
+        <v>708</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>46225.00753472222</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>46225.00755787037</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>46225.00841435185</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf27d724-418f-49d1-9a0c-6f51ee1cc37b              </t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885ff320-668f-4117-a502-601d625621e8              </t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>ca este código con nadie.</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>76</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>76 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>23119970</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>50492463599</v>
+      </c>
+      <c r="F39" t="n">
+        <v>708</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>46225.00753472222</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>46225.00755787037</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>46225.00841435185</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c39a3e00-7e94-4657-a926-944cd4568290              </t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295d2397-13a6-4523-9a33-4e6b5f2a71b8              </t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Docusign es 559012. Por motivos de seg</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>76</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>76 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>23119970</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>50492463599</v>
+      </c>
+      <c r="F40" t="n">
+        <v>708</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>46225.00753472222</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>46225.00755787037</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>46225.00841435185</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68363c87-333a-43d5-84a2-65a9f9e8dcd0              </t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308cf4e8-25ac-494c-8d6a-a89106a5149b              </t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>uridad, no utilices este código fuera de Docusign. No compartas nun</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>76</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>76 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>23119969</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>56936858166</v>
+      </c>
+      <c r="F41" t="n">
+        <v>730</v>
+      </c>
+      <c r="G41" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>WOM sa (Novator Partners)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>RQVXVZ</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>46225.00752314815</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>46225.0075462963</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46225.00756944445</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3f59beb0-6ca9-49c9-a073-1265a7a89ea3              </t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4d890ed2-5e59-4249-8d01-96f53d2cee0d              </t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>¡Reclama 30 giros gratis en Sugar Rush 1000 por activar tu correo! Detalles https://1xcas.net/naHns6h</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>4 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>23119968</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>85587392121</v>
+      </c>
+      <c r="F42" t="n">
+        <v>456</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>46225.00690972222</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>46225.00693287037</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>46225.00701388889</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83bf0e35-d93f-4634-a4bd-f3bd8e9793c9              </t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ad280330-a454-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Your verification code is 8342, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>9 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>23119967</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>85570211311</v>
+      </c>
+      <c r="F43" t="n">
+        <v>456</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>46225.00673611111</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>46225.00675925926</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>46225.006875</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">397f2052-7713-46c7-839c-4124410ae517              </t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a4272a88-a454-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Your verification code is 244677, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>23119966</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>447877778404</v>
+      </c>
+      <c r="F44" t="n">
+        <v>234</v>
+      </c>
+      <c r="G44" t="n">
+        <v>20</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>46225.00553240741</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>46225.00555555556</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>46225.00572916667</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4472c6ab-d2d3-4be6-b266-09542fdaaa90              </t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5325d55-e65d-40f9-934e-09a55a06826e              </t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Hi there. 058 451</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>23119965</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>85515355792</v>
+      </c>
+      <c r="F45" t="n">
+        <v>456</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>46225.00216435185</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>46225.00217592593</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>46225.00225694444</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7e45e34d-ccfd-4708-a246-64e1ec6f43c1              </t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b84eda34-a453-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Your verification code is 5779, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>8 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>23119964</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>447883859244</v>
+      </c>
+      <c r="F46" t="n">
+        <v>234</v>
+      </c>
+      <c r="G46" t="n">
+        <v>20</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>46225.00192129629</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>46225.00193287037</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>46225.00210648148</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78797659-acef-43ae-90ce-ddba2bbde8d3              </t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fd099310-b10c-4fd6-ac57-ba4e6427fc6e              </t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Hi there. 082 911</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>23119963</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5511952360646</v>
+      </c>
+      <c r="F47" t="n">
+        <v>724</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CUBIC TELECOM BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>SUPERPROF</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>46225.00144675926</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>46225.00145833333</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>46225.00165509259</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>52</v>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8445d559-f80c-4528-af3e-a93dd81d162b              </t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9362828c-a453-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Seu codigo de verificacao
+ @superprof.com.br #539926</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>23119962</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>447481827035</v>
+      </c>
+      <c r="F48" t="n">
+        <v>234</v>
+      </c>
+      <c r="G48" t="n">
+        <v>20</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>46225.00135416666</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>46225.00137731482</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>46225.00155092592</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3221936a-c15a-400a-9b66-8eea1e5e89b3              </t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5a10744-1e5e-49b9-b5ff-3348bf745813              </t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Hi there. 182 964</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>23119961</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>447707475453</v>
+      </c>
+      <c r="F49" t="n">
+        <v>234</v>
+      </c>
+      <c r="G49" t="n">
+        <v>10</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>46225.00027777778</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>46225.00030092592</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>46225.00054398148</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b50f563d-bff2-49be-9c78-a75385236938              </t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66f71776-c60b-44ed-a7a5-dfc404364e40              </t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Hi there. 635 921</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,5389 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23185397</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447970801089</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46226.02890046296</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46226.02892361111</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46226.02908564815</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0e7ef9d6-a39e-4ce2-8b1e-c879ec9af9aa              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecbe5c0d-6239-4298-ad23-171636b2ca6c              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 958 494</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23185396</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>85515294686</v>
+      </c>
+      <c r="F3" t="n">
+        <v>456</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46226.02885416667</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46226.02887731481</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46226.02894675926</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b9dfd4b1-9c28-4732-beea-10049e03057b              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41618ecc-a522-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Your verification code is 9078, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>8 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23185395</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447834949893</v>
+      </c>
+      <c r="F4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46226.02809027778</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46226.02810185185</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46226.02826388889</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b88c5ee5-211d-44c1-a9fc-aca6e4e7bc2a              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ca18b21e-365d-413c-a84a-c3e15f72d56d              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hi there. 560 998</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23185394</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447884965768</v>
+      </c>
+      <c r="F5" t="n">
+        <v>234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46226.0278125</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46226.02783564815</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46226.02799768518</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123b0366-ad8b-4eca-a317-0688e3e12415              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cbae44e5-3a72-4891-873c-4a7b83362d25              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Hi there. 352 919</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23185393</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>447403784822</v>
+      </c>
+      <c r="F6" t="n">
+        <v>234</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46226.02760416667</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46226.02762731481</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46226.02777777778</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c08c440f-98a3-4675-a220-c57791209f8a              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ecc3c7b-d96a-441f-8424-c16540e2d953              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Hi there. 946 737</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23185392</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>447782827695</v>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46226.02743055556</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46226.0274537037</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46226.02760416667</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33e11f3c-f9cb-409b-8cd1-11be8f78ede7              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138b4815-2802-4083-b14d-436c56882bf6              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hi there. 409 080</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23185391</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447414868396</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46226.02743055556</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46226.0274537037</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46226.02760416667</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7a32cf19-e30b-4936-a84c-936dc63c1230              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b2b7bc13-a4de-48ab-817f-f59035ee67af              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 192 660</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23185390</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447456055517</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46226.02679398148</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46226.0268287037</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46226.02697916667</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35e86858-cf36-48a9-8893-3232ae77f12b              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c9b2c07d-7707-4b0b-94d5-81d2a28bc6c6              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 992 727</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23185389</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>447463921578</v>
+      </c>
+      <c r="F10" t="n">
+        <v>234</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46226.02652777778</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46226.02655092593</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46226.02672453703</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3e175ba6-23a5-4bf4-bcd0-3f640496fc54              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64bbf7c5-9d5b-4ebb-aad5-05f57a8faae2              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Hi there. 908 278</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23185388</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>447957333660</v>
+      </c>
+      <c r="F11" t="n">
+        <v>234</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46226.02631944444</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46226.0263425926</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46226.02649305556</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7905393d-9519-4187-890f-ee3b88203af8              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f7ce050d-dd4b-453e-86f1-3de0306239f8              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Hi there. 720 184</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23185387</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447789222101</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46226.02461805556</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46226.02462962963</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46226.02479166666</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2a39de9e-6c1d-4fdc-b0b2-1570bc316326              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1d439726-a9f9-4bbb-91e3-82a8c4e1b0eb              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 357 897</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23185386</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>447426471946</v>
+      </c>
+      <c r="F13" t="n">
+        <v>234</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46226.02409722222</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46226.02412037037</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46226.02429398148</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0885d733-8334-42bb-8e5a-32a76ccd22f4              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2f15746d-0184-438e-b3e2-6dacd8713ad6              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Hi there. 189 722</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23185385</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>447943002877</v>
+      </c>
+      <c r="F14" t="n">
+        <v>234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46226.02380787037</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46226.02381944445</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46226.02399305555</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09f9b90b-d3e6-4dd8-9da6-3e41ec08e819              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b91e8d6a-65da-42ad-bfb9-39aaf1620f73              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Hi there. 376 118</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23185384</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>447426471946</v>
+      </c>
+      <c r="F15" t="n">
+        <v>234</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46226.02261574074</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46226.02263888889</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46226.02280092592</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cbafb75d-f3b1-4ca2-947a-0be87b8b7a6d              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e6f66093-cebd-4eaa-a32d-e65e81842f87              </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Hi there. 336 734</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23185383</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>56940383070</v>
+      </c>
+      <c r="F16" t="n">
+        <v>730</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Entel PCS Telecomunicaciones sa</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>UBRBPE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46226.02153935185</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46226.0215625</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46226.02158564814</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f1cdb51d-eeaf-47a7-839e-21a1eb6b7192              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d884bbb5-ffdc-49ec-9591-244074d31c5f              </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>¡Reclama 30 giros gratis en Sugar Rush 1000 por activar tu correo! Detalles https://1xcas.net/naHns6h</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>4 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23185382</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>447883592156</v>
+      </c>
+      <c r="F17" t="n">
+        <v>234</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46226.01913194444</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46226.01914351852</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46226.0193287037</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fa0a9be2-ebbb-40ca-aebc-cca7e9191d00              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">379b4934-24d6-4ece-aae5-7339d2c8e26d              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Hi there. 026 010</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23185381</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>447488705996</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46226.01856481482</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46226.01858796296</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46226.01876157407</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9904c3fb-4c30-4e91-be38-158207f09aba              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08e7f165-8726-46d2-83e0-9014df900b0e              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Hi there. 171 225</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23185380</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>447395661999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>234</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46226.01847222223</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46226.01849537037</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46226.01865740741</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75aaef08-990f-4691-8ff8-28d17d47069e              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0d9a9de9-3876-4be8-95d7-929f932cec6d              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Hi there. 775 052</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23185379</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>447428519207</v>
+      </c>
+      <c r="F20" t="n">
+        <v>234</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46226.01841435185</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46226.0184375</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46226.01859953703</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6de220fa-8d62-4663-9056-77a62b48adc4              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6de5e6b-31a2-4098-83ad-67981479ede6              </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Hi there. 885 109</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23185378</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>447488705996</v>
+      </c>
+      <c r="F21" t="n">
+        <v>234</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46226.01773148148</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46226.01774305556</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46226.01790509259</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231870c5-718c-42b4-81d4-33cd622d7a5c              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d8e8316a-a702-4136-bedd-6b3a68f40f74              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Hi there. 927 940</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23185377</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>56973780451</v>
+      </c>
+      <c r="F22" t="n">
+        <v>730</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Entel PCS Telecomunicaciones sa</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FUBGTK</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46226.01598379629</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46226.01600694445</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46226.01604166667</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">496cb0e9-2e62-40bf-92d6-9db5908c026e              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230e7549-1f49-4ed5-b091-ece89a85c280              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>¡Reclama 30 giros gratis en Sugar Rush 1000 por activar tu correo! Detalles https://1xcas.net/naHns6h</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>5 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23185376</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5583991657557</v>
+      </c>
+      <c r="F23" t="n">
+        <v>724</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46226.01506944445</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46226.01509259259</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>46226.01523148148</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abe7dd0e-4d78-4b97-9d32-6223ee65f191              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7b9e0ad0-a51f-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Use o codigo 573788 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23185375</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>447737823503</v>
+      </c>
+      <c r="F24" t="n">
+        <v>234</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46226.01256944444</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46226.01259259259</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46226.01275462963</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf40c565-e6f2-4a99-9382-bdd0f0dad242              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fa134b15-4e4c-4b89-ac1e-57e36639fe45              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Hi there. 450 084</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23185374</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>447904531207</v>
+      </c>
+      <c r="F25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G25" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46226.01099537037</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46226.01101851852</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46226.01119212963</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85937061-7382-4ac2-bcd2-bc739cf6af1e              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1b4c06c2-a65a-4fc0-999d-b7600a490d00              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Hi there. 640 871</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23185373</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>56955148972</v>
+      </c>
+      <c r="F26" t="n">
+        <v>730</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Nextel sa (WOM)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>LJLEGO</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46226.01043981482</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46226.01045138889</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>46226.01047453703</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2c783f79-8d24-419b-aac4-bb1e749bf92e              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de76a963-1ea4-4daa-8a21-611e0f032543              </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>¡Reclama 30 giros gratis en Sugar Rush 1000 por activar tu correo! Detalles https://1xcas.net/naHns6h</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>3 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23185372</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>51927778688</v>
+      </c>
+      <c r="F27" t="n">
+        <v>716</v>
+      </c>
+      <c r="G27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46226.00991898148</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46226.00998842593</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46226.01</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9d4913af-6365-4453-8c8a-c90fc1f83967              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89a3f0cd-ed80-4834-9787-e1e304e8ca84              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 4504
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23185371</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>447403984250</v>
+      </c>
+      <c r="F28" t="n">
+        <v>234</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46226.00917824074</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46226.00918981482</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46226.00935185186</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2b4e63b2-3856-426d-b3df-90687a62976f              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71368aa0-3819-4621-9496-06bfff636250              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Hi there. 936 166</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23185370</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>56959904233</v>
+      </c>
+      <c r="F29" t="n">
+        <v>730</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Claro Chile sa</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>QNZJXP</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>46226.00905092592</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>46226.0090625</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>46226.00909722222</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0d01c5ed-2020-4bad-901a-a323a06a4fbf              </t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520c880f-a64b-4d8c-a972-2b68ce00cac2              </t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>¡Reclama 30 giros gratis en Sugar Rush 1000 por activar tu correo! Detalles https://1xcas.net/naHns6h</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>4 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23185369</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>447908719982</v>
+      </c>
+      <c r="F30" t="n">
+        <v>234</v>
+      </c>
+      <c r="G30" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>46226.00848379629</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>46226.00849537037</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>46226.00865740741</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fa9a2f68-1025-4c29-9c76-89576aa47c4c              </t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d649138e-942c-4ded-bcd5-9a8b16521288              </t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Hi there. 124 775</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>23185368</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>447465671797</v>
+      </c>
+      <c r="F31" t="n">
+        <v>234</v>
+      </c>
+      <c r="G31" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>46226.00806712963</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>46226.00809027778</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>46226.00826388889</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b014cc66-adaf-4d71-b1b7-f6e8d5e7f59d              </t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6e93791e-5ede-4e13-b600-b66bd59a5b36              </t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Hi there. 720 833</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>23185367</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TEXT2WORLD PTE LIMITED.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>85578342716</v>
+      </c>
+      <c r="F32" t="n">
+        <v>456</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CellCard</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>TIGER</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>46226.00763888889</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>46226.00765046296</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>46226.00799768518</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c08214f0-07ad-4318-b05e-b97d89dcab1a              </t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fca29460-a51d-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Your verification code is 3569, please do not share it with others.</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>31 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>23185366</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>447916368110</v>
+      </c>
+      <c r="F33" t="n">
+        <v>234</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>46226.00605324074</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>46226.00612268518</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>46226.00627314814</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f4a1f9e8-4a5d-40ff-aac5-333734e637df              </t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25413f0d-738a-4b15-9a63-5243650fb24f              </t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Hi there. 155 296</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>23185365</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>447482265566</v>
+      </c>
+      <c r="F34" t="n">
+        <v>234</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>46226.00579861111</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>46226.00581018518</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>46226.0059837963</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115253e6-61f5-4908-adae-7b92ed9e8cb1              </t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d9ad392f-dfe7-48f6-8200-25c8c306398b              </t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Hi there. 765 691</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>23185364</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>447577609633</v>
+      </c>
+      <c r="F35" t="n">
+        <v>234</v>
+      </c>
+      <c r="G35" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>46226.00475694444</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>46226.00476851852</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46226.00493055556</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ee81a362-0e36-420b-9137-7d61fd693fbf              </t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e2548f34-6055-44b9-a67e-dbc014b39365              </t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Hi there. 023 351</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>23185363</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>447971964752</v>
+      </c>
+      <c r="F36" t="n">
+        <v>234</v>
+      </c>
+      <c r="G36" t="n">
+        <v>33</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>46226.0042824074</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>46226.00430555556</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46226.00447916667</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259466e5-1263-4ead-93b5-ae3a1b8fea20              </t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9dbc9c40-d3c5-4b1d-9a6e-75202271f95c              </t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Hi there. 490 901</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>23185362</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>447473588889</v>
+      </c>
+      <c r="F37" t="n">
+        <v>234</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>46226.00239583333</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>46226.00243055556</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46226.00260416666</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3d98925d-178a-4346-852d-1842bdcb0aee              </t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9d9a6484-111b-4428-bb2e-09c7bfbafd6b              </t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Hi there. 642 491</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>23185361</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>447877853076</v>
+      </c>
+      <c r="F38" t="n">
+        <v>234</v>
+      </c>
+      <c r="G38" t="n">
+        <v>20</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>46226.00225694444</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>46226.00228009259</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>46226.0024537037</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1705071e-5f09-43c2-ba9e-2e3e2d4ce607              </t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5280bb44-a893-4769-9d3f-a248af4ea5a1              </t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Hi there. 083 214</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>23185360</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>447540117725</v>
+      </c>
+      <c r="F39" t="n">
+        <v>234</v>
+      </c>
+      <c r="G39" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>46226.00201388889</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>46226.00203703704</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>46226.00221064815</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c65d8029-fb0b-46f4-8844-340c87c8dce4              </t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cc30c80f-50bd-4869-bf37-050786eac8eb              </t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Hi there. 183 271</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>23185359</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>447736093221</v>
+      </c>
+      <c r="F40" t="n">
+        <v>234</v>
+      </c>
+      <c r="G40" t="n">
+        <v>10</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>46226.000625</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>46226.00064814815</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>46226.00079861111</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62733432-b8b7-4058-a922-06814806949a              </t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9bb04d43-0731-4e38-91c9-40082ee730a7              </t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Hi there. 932 566</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,4285 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23287773</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447886665548</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46227.02625</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46227.02630787037</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46227.02645833333</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19f1a1e3-d654-44f2-8006-6f166119f5a6              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3d349386-69ea-480c-98dc-d520cc346039              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 019 504</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23287772</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>447492004743</v>
+      </c>
+      <c r="F3" t="n">
+        <v>234</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46227.02603009259</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46227.02605324074</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46227.02621527778</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692fe099-33a0-4d1d-a040-68167f8c39f8              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75ab0a15-767d-40b9-a970-ed1a78d61f75              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Hi there. 106 882</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23287771</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>59169130964</v>
+      </c>
+      <c r="F4" t="n">
+        <v>736</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>NOTICE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46227.02469907407</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46227.02473379629</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46227.02489583333</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">776d74ae-9ce6-44ca-b83f-19d2eca58010              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">967506c0-a5ea-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>228101 es su código de verificación COSMart</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23287770</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447519939110</v>
+      </c>
+      <c r="F5" t="n">
+        <v>234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46227.02429398148</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46227.02431712963</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46227.02447916667</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601f748c-a5da-43ee-b7b6-52154cfb7db0              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1c636ab1-f85c-4f8d-ab3d-73a98912354d              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Hi there. 770 744</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23287769</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>447490909004</v>
+      </c>
+      <c r="F6" t="n">
+        <v>234</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46227.02364583333</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46227.02365740741</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46227.02383101852</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d2af22b1-739b-41a5-9385-e99f0f040f10              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c28d32f3-6b97-43eb-b192-536aa2e9655b              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Hi there. 768 589</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23287768</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>447449936817</v>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46227.02355324074</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46227.02358796296</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46227.02375</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5f918fd3-34b4-45d8-ac1d-7354c27795c8              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d96c29a8-1845-437d-b21f-f14856242ff5              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hi there. 235 553</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23287767</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447792912364</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>33</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46227.02336805555</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46227.0233912037</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46227.02356481482</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e1955946-5a06-4c2a-979a-b96a9f94464c              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15bb9556-0a40-4f76-ba14-c27b74c251ec              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 995 428</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23287766</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447403222638</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46227.02334490741</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46227.02336805555</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46227.02353009259</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b18662d1-fcfa-4ffd-932f-58c6534aabc2              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8b78f2e1-e7ca-4c7d-8129-13a3318f7f09              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 445 292</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23287765</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>51930157858</v>
+      </c>
+      <c r="F10" t="n">
+        <v>716</v>
+      </c>
+      <c r="G10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46227.02296296296</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46227.02306712963</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46227.02306712963</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a7575792-eedd-4bd4-a848-8e7e81ca138d              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f3b6bccf-d9cb-43ee-8718-02a67f90aee6              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 8689
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>9 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23287764</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>447462253497</v>
+      </c>
+      <c r="F11" t="n">
+        <v>234</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46227.02295138889</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46227.02297453704</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46227.02313657408</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">038018c7-1ee2-43e9-882a-009142dfdf9d              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">630909d3-9e26-4317-b2ad-8dc12b94bf1e              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Hi there. 935 404</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23287763</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447397969079</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46227.02271990741</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46227.02274305555</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46227.02289351852</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9672f618-0cba-4ad6-8050-e7934a65d3d1              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f681b58f-3293-4340-bc98-003c6e1b3fc9              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 158 417</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23287762</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>447450271233</v>
+      </c>
+      <c r="F13" t="n">
+        <v>234</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46227.02173611111</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46227.02177083334</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46227.0219212963</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47b58ae1-c952-49dc-9b21-5ff0857826ae              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21e3327e-bd73-4a9d-9c54-c58dc94a3264              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Hi there. 106 828</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23287761</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5521977453205</v>
+      </c>
+      <c r="F14" t="n">
+        <v>724</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46227.02138888889</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46227.02141203704</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46227.02145833334</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276bff25-b65a-4caf-bce4-dfde0c889867              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eb77bc0c-a5e9-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Use o codigo 559639 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23287760</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>447449936817</v>
+      </c>
+      <c r="F15" t="n">
+        <v>234</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46227.02041666667</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46227.02045138889</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46227.020625</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc8c43e2-35c4-4a97-b005-c8dc6fc72d91              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79b5ef55-a49c-4f6d-868e-c8fe99b39c07              </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Hi there. 271 954</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23287759</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>447886165191</v>
+      </c>
+      <c r="F16" t="n">
+        <v>234</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46227.01856481482</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46227.01857638889</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46227.01876157407</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2921dd61-03c9-4de3-a706-60fe47d20f7a              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6d684115-09d6-49f5-a9cb-7b7d3c2a8413              </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Hi there. 274 303</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23287758</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>447912227650</v>
+      </c>
+      <c r="F17" t="n">
+        <v>234</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46227.01841435185</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46227.0184375</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46227.01859953703</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">024613fb-dbf0-470c-b853-4e79e3270f23              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0ca2095d-88a7-41a8-b5f5-b42943a31903              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Hi there. 507 784</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23287757</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>447480331944</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46227.01637731482</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46227.01640046296</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46227.01655092592</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38ab4e83-ef7a-41ff-9498-f6f25f657b5e              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5c867748-ac1d-40bd-909c-9f9fa8fd0a02              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Hi there. 917 096</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23287756</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>447850995855</v>
+      </c>
+      <c r="F19" t="n">
+        <v>234</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46227.0134375</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46227.01346064815</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46227.01363425926</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2c22d6c4-9d66-477d-b491-41fd0e8cfecd              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71e5cf67-80b4-498b-8e3b-56a816172d84              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Hi there. 322 313</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23287755</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>447311470227</v>
+      </c>
+      <c r="F20" t="n">
+        <v>234</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46227.0125</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46227.01252314815</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46227.01269675926</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97ff6c46-efd0-472b-bbf5-d05b78edda2d              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9203b749-a181-466c-963a-90a5696422be              </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Hi there. 115 483</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23287754</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>447490399749</v>
+      </c>
+      <c r="F21" t="n">
+        <v>234</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46227.0122337963</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46227.01225694444</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46227.01244212963</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7c0d9cfe-2a1c-4950-bd0d-c28564aa5913              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">012ddd3b-6214-438e-9d9a-fff316ce68aa              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Hi there. 085 551</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23287753</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>447475619554</v>
+      </c>
+      <c r="F22" t="n">
+        <v>234</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46227.01039351852</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46227.01041666666</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46227.01059027778</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22e0e6b1-8272-451b-a2ab-818316684ba9              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0e005610-9815-46c4-9bc2-2a97fa167543              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Hi there. 821 304</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23287752</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>447869839318</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46227.00787037037</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46227.00790509259</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>46227.00805555555</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a3ab8013-f933-4c9f-a374-e659f431ba93              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ef44395a-69b1-4de7-97ca-0612e28c3def              </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Hi there. 548 484</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23287751</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>447916988022</v>
+      </c>
+      <c r="F24" t="n">
+        <v>234</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46227.00635416667</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46227.00640046296</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46227.00657407408</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cbd80cc9-48f1-49a6-a21a-a983c3bf9ff7              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74ef430e-b224-4f61-8d38-c0ec066ceae2              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Hi there. 449 213</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23287750</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>447861271077</v>
+      </c>
+      <c r="F25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46227.00550925926</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46227.00554398148</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46227.00571759259</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0356db54-aa4c-463d-82bd-22063305b4b2              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9a249776-c7b8-4566-b738-25b7344aa8bf              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Hi there. 301 194</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23287749</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5511993213383</v>
+      </c>
+      <c r="F26" t="n">
+        <v>724</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46227.0053125</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46227.00533564815</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>46227.00549768518</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86e29393-9132-42bd-aacf-02601c91dbbf              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aff43210-a5e6-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Use o codigo 487360 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23287748</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>447861271077</v>
+      </c>
+      <c r="F27" t="n">
+        <v>234</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46227.0047337963</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46227.00475694444</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46227.00493055556</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">831cc57b-a80a-4e93-89a3-a11c02c2d764              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">390bf97a-7133-40ff-8663-b0e8087e19c2              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Hi there. 939 511</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23287747</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>447882372612</v>
+      </c>
+      <c r="F28" t="n">
+        <v>234</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46227.00443287037</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46227.00444444444</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46227.00461805556</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f99bec69-670e-47f1-b351-62d109786a8d              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2302cc29-b8ca-41ef-89d5-dde74ee8f471              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Hi there. 329 414</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23287746</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>447402890507</v>
+      </c>
+      <c r="F29" t="n">
+        <v>234</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>46227.00420138889</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>46227.00422453704</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>46227.00438657407</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">441193c1-27db-4791-a5a0-2f5611603a7c              </t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">032ef053-7a1a-4963-8fe4-b752f6ee52f3              </t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Hi there. 727 809</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23287745</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>447307126028</v>
+      </c>
+      <c r="F30" t="n">
+        <v>234</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>46227.00189814815</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>46227.00192129629</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>46227.00209490741</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5daec75a-ac4f-4251-82dd-5c316cfb1d85              </t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00230af1-4c86-4db7-a5cc-8d6842895793              </t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Hi there. 315 845</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>23287744</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>51974656774</v>
+      </c>
+      <c r="F31" t="n">
+        <v>716</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CLARO(AMERICA MOVIL PERU S.A.C.)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>46227.00184027778</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>46227.00188657407</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>46227.00189814815</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4b066952-37fa-4ae1-ab62-4b09526cb911              </t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">670c5c68-1a53-473e-98ce-b0cd165c99fd              </t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>inDrive code: 4085</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>5 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>23287743</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>447404631370</v>
+      </c>
+      <c r="F32" t="n">
+        <v>234</v>
+      </c>
+      <c r="G32" t="n">
+        <v>26</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Lycamobile UK Limited</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>46227.00016203704</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>46227.00017361111</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>46227.00034722222</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5e24c37-b70b-4fd0-8ad4-c1114cfab7c6              </t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">832ef1d0-558b-4957-a19a-35a774abd515              </t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Hi there. 754 572</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,4015 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23295441</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447501581840</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46228.02305555555</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46228.02309027778</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46228.02325231482</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f6a6dddb-a019-47c7-81d7-2f11ffecd3bc              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89481190-2541-424e-90ca-acd9d08adae3              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 653 483</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23295440</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>447572267030</v>
+      </c>
+      <c r="F3" t="n">
+        <v>234</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46228.02180555555</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46228.02182870371</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46228.02202546296</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b9aca6ca-eb0f-478a-be70-e12aa4652a7d              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9f96388e-96a6-4da0-a58a-d3cf90a5665b              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Hi there. 486 024</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23295439</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447853336029</v>
+      </c>
+      <c r="F4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46228.02122685185</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46228.02126157407</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46228.02151620371</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20c47ac4-7f0b-4267-8846-2802265777e7              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c7577b98-e1d2-4cc7-9b3a-ebe5036fbcba              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hi there. 915 914</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>25 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23295438</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447979971982</v>
+      </c>
+      <c r="F5" t="n">
+        <v>234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46228.02070601852</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46228.02072916667</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46228.02084490741</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56cd5ef9-648f-41c5-b3d0-4243a3e3ea50              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7282b426-dbcd-4562-b0c0-87d66473ec94              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Hi there. 226 748</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23295437</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>447729985003</v>
+      </c>
+      <c r="F6" t="n">
+        <v>234</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46228.02059027777</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46228.02061342593</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46228.02074074074</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9faa1ebc-5a91-47f0-93a4-1e92bf94385b              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6b168a99-e179-4994-8ef8-41fa659ff53e              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Hi there. 603 439</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23295436</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>447944782132</v>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46228.02055555556</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46228.0205787037</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46228.02074074074</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">343cc793-9371-43ee-9642-b472cb139b7f              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3122129e-2184-48af-80f7-70049e5f0cc3              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hi there. 270 011</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23295435</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447572570175</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46228.01893518519</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46228.01895833333</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46228.0190625</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1edc6bff-4157-4ee5-9927-d147f32967ea              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">af5989a0-cc28-4670-aa0c-4357b33ff999              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 862 791</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23295434</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447309785992</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46228.01835648148</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46228.01837962963</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46228.0185300926</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84d440a4-de41-4c5d-ac6f-1d1639877739              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d7b75d86-20c0-4cd5-944b-3c29ad9ee20d              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 504 834</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23295433</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>447378129854</v>
+      </c>
+      <c r="F10" t="n">
+        <v>234</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46228.01806712963</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46228.01810185185</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46228.01832175926</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a7792e3-bd75-4814-b0fc-fb3d98d1dfc7              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a91b00d8-3be9-4d9d-911d-7abda497b73a              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Hi there. 954 165</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23295432</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>447586753192</v>
+      </c>
+      <c r="F11" t="n">
+        <v>234</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46228.01771990741</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46228.0177662037</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46228.01788194444</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c43c5319-d9bf-4c4f-8804-283fb7f533d3              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e468ba3a-99cf-4d0a-af39-a8ce1d791ca7              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Hi there. 345 719</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23295431</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447828650164</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46228.01717592592</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46228.01719907407</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46228.01741898148</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f82763b3-1076-43cd-b6cf-858d321a5b1f              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108d8a74-3d46-4c75-8ce9-8cec81e325f6              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 818 795</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23295430</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>447898857756</v>
+      </c>
+      <c r="F13" t="n">
+        <v>234</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46228.01695601852</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46228.01699074074</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46228.01717592592</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5352b6da-c880-4f90-949c-fea3a2ff2881              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67330a3e-a725-459b-8195-d3b07eca1b1f              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Hi there. 066 601</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23295429</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>447465723923</v>
+      </c>
+      <c r="F14" t="n">
+        <v>234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46228.01578703704</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46228.01581018518</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46228.0159375</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">443d8b55-2325-42fe-8b0f-c1e0873afdee              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7da7bbc0-f3cc-4b77-8d58-ce6dbdcb3c57              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Hi there. 824 109</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23295428</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>447531544029</v>
+      </c>
+      <c r="F15" t="n">
+        <v>234</v>
+      </c>
+      <c r="G15" t="n">
+        <v>33</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46228.01487268518</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46228.01489583333</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46228.01512731481</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0cec9606-a6d9-41b1-8640-d28e4293cd03              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d9abeed5-ab94-4473-af91-7b38f267e06a              </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Hi there. 016 109</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23295427</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>447895409516</v>
+      </c>
+      <c r="F16" t="n">
+        <v>234</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46228.01450231481</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46228.01452546296</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46228.01479166667</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58fb1bc9-f2d6-459e-ac69-6f6995f5a049              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23859d83-9c2d-4558-b3b5-1356c7289b7d              </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Hi there. 744 967</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>25 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23295426</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>447403832626</v>
+      </c>
+      <c r="F17" t="n">
+        <v>234</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46228.01438657408</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46228.01440972222</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46228.0146875</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8f16132e-3ce6-461d-9fc1-bbf389d60eb8              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43da29d3-7b66-4dec-850b-3801805b69db              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Hi there. 131 754</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>26 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23295425</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>447969398727</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>33</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46228.0124074074</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46228.01243055556</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46228.01262731481</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">383831b0-07d2-491e-b862-2d72d55f9be9              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b230a3eb-c813-4c99-820f-8f2050dddc8d              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Hi there. 204 149</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23295424</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>447969398727</v>
+      </c>
+      <c r="F19" t="n">
+        <v>234</v>
+      </c>
+      <c r="G19" t="n">
+        <v>33</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46228.0121412037</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46228.0121875</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46228.01247685185</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4d70d88e-f6ab-4278-b35e-7f85e727db42              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980d4299-83ff-41b9-8cc8-e99f35d2bcdf              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Hi there. 480 506</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>29 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23295423</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>51982218721</v>
+      </c>
+      <c r="F20" t="n">
+        <v>716</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CLARO(AMERICA MOVIL PERU S.A.C.)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46228.01206018519</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46228.01210648148</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46228.01211805556</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ec89687-71a3-4b87-895b-f6b8f4cbcdf0              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28c51cf3-5f3e-408f-acb4-946423828d65              </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 8417
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>5 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23295422</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5531986071444</v>
+      </c>
+      <c r="F21" t="n">
+        <v>724</v>
+      </c>
+      <c r="G21" t="n">
+        <v>31</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>OI S.A. (TNL PCS S.A.)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>myCicero</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46228.01172453703</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46228.01175925926</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46228.01184027778</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3dbac100-40bd-4969-a22b-49451ebc62f6              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24d492a0-a6b1-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Activation PIN: 805540 - Account : arthurpinheirobh@gmail.com.
+ @ #805540</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23295421</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>447853179129</v>
+      </c>
+      <c r="F22" t="n">
+        <v>234</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46228.01049768519</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46228.01053240741</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46228.01072916666</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261aee82-978a-40b4-8f07-955f04151ab9              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b3ee3059-0d9d-4322-a592-9d0b428e3790              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Hi there. 293 021</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23295420</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>447927219291</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46228.00532407407</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46228.00534722222</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>46228.00559027777</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96b08fdd-eec0-4f7f-b67c-734c7968f3f0              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9d4adba2-12bf-4211-98ea-a72116fc6ba4              </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Hi there. 929 404</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23295419</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>447853011551</v>
+      </c>
+      <c r="F24" t="n">
+        <v>234</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46228.00518518518</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46228.00520833334</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46228.00539351852</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7de79026-e272-4eca-8d19-b04885833395              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d61db7e9-9de6-4e4d-b539-25af00f010e2              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Hi there. 832 319</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23295418</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>447988098269</v>
+      </c>
+      <c r="F25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46228.00390046297</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46228.00393518519</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46228.0040625</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f71f7513-eba7-4b15-a26f-ed9cc6ece5e7              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8c55c885-d1ea-49bd-9a14-5624fd5b70f6              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Hi there. 463 503</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23295417</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>447480923436</v>
+      </c>
+      <c r="F26" t="n">
+        <v>234</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46228.00340277778</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46228.00342592593</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>46228.00356481481</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e02c8599-99e7-4a04-94f9-fd86016eebb5              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">487a081c-96de-4b7e-9ab7-b9cbffc259bc              </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Hi there. 248 008</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23295416</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5522998065218</v>
+      </c>
+      <c r="F27" t="n">
+        <v>724</v>
+      </c>
+      <c r="G27" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VIVO S.A.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>myCicero</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46228.00269675926</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46228.00273148148</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46228.00289351852</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>82</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e97a0113-4251-43f4-9a36-514544096dc4              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53f63e28-a6af-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Activation PIN: 501161 - Account : barbaramendescastelar@yahoo.com.br.
+ @ #501161</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23295415</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>447575855546</v>
+      </c>
+      <c r="F28" t="n">
+        <v>234</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46228.00097222222</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46228.00100694445</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46228.00112268519</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3e35262a-abdb-41b8-9fe4-7af5eb25866f              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6211b324-c62d-4a99-8ccf-1845be55d2e0              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Hi there. 952 494</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23295414</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>447727867648</v>
+      </c>
+      <c r="F29" t="n">
+        <v>234</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>46228.00035879629</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>46228.00039351852</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>46228.00050925926</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8102ad8f-3cb7-42bf-8b2e-953b3f3e5178              </t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">741fd695-2ef4-4fd5-9fe9-23d9491eace7              </t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Hi there. 837 278</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23295413</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>447575855546</v>
+      </c>
+      <c r="F30" t="n">
+        <v>234</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>46228.00008101852</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>46228.00010416667</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>46228.00023148148</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a1dfdddb-dcd0-466f-9a7b-caa584fc0736              </t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c300b101-7034-40a7-b6c0-0aec94e3076d              </t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Hi there. 486 052</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,5390 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23301660</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447970721940</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46229.03314814815</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46229.03317129629</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46229.03331018519</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9768ad04-c663-4110-86de-a2e7e8ee060c              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5d665b9-1dd7-407e-9e15-323dcb87f0d2              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 701 509</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23301659</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>447951504743</v>
+      </c>
+      <c r="F3" t="n">
+        <v>234</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46229.03287037037</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46229.03289351852</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46229.03318287037</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e0d9a0da-e847-4e97-a10c-37f04fe3e4f9              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1e6b356-0164-4be8-bf84-f26fd02cf57c              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Hi there. 383 191</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>27 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23301658</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447737015940</v>
+      </c>
+      <c r="F4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46229.03282407407</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46229.03284722222</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46229.03304398148</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26bcf726-e434-4876-9715-4f74a082708a              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8db64cc6-0959-49b9-957a-2b7bf60ee4ce              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hi there. 771 553</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23301657</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447737015940</v>
+      </c>
+      <c r="F5" t="n">
+        <v>234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46229.03178240741</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46229.03180555555</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46229.03206018519</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71dbbb53-a5b9-4edf-a60b-1ea526c61409              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e2e5ce99-d21d-4558-9fcb-47eec5fbbb63              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Hi there. 638 228</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>24 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23301656</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>447951504743</v>
+      </c>
+      <c r="F6" t="n">
+        <v>234</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46229.03146990741</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46229.03149305555</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46229.03168981482</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d6756d9f-6f50-4410-bc04-c7e255e15e55              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0e22216f-a588-4781-9a96-8461126e66cf              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Hi there. 134 207</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23301655</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>447490927680</v>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46229.03039351852</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46229.03040509259</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46229.03064814815</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bcc7a82a-250f-4709-84f3-a9a321af4c4a              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a1b51ecf-836f-44e2-ba9f-a457b1849ad0              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hi there. 302 294</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23301654</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447378129854</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46229.03028935185</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46229.0303125</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46229.03055555555</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0761225f-4631-415f-85c7-d8f7d82cf8bd              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">385f01c5-494f-403c-88bb-e79893a6aa71              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 055 306</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23301653</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447403536409</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46229.02969907408</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46229.02972222222</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46229.02990740741</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c968e712-f8ae-4fdf-81e7-96cd4cc23411              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698bc811-d4e9-4da9-9095-5470cf418a97              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 747 811</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23301652</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>447882794147</v>
+      </c>
+      <c r="F10" t="n">
+        <v>234</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46229.02880787037</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46229.02881944444</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46229.0290625</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f91f01a9-b657-4250-9492-4a247c7d9d2d              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e49db574-a6d9-43b4-91d1-1f2408b25cfe              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Hi there. 613 170</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23301651</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>447876045678</v>
+      </c>
+      <c r="F11" t="n">
+        <v>234</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46229.0278125</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46229.02783564815</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46229.02796296297</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">003a240c-d94d-4661-bf8b-8eea1b7dda14              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80de554c-c904-4751-8e33-a097609f706a              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Hi there. 727 039</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23301650</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447706267250</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46229.02599537037</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46229.02601851852</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46229.02626157407</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fb8c1706-0034-4bda-9d13-755cbbd82c72              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80acf604-3a5e-4f54-b316-02d5d58ea5a6              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 678 459</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23301649</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>447308659995</v>
+      </c>
+      <c r="F13" t="n">
+        <v>234</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46229.02579861111</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46229.02581018519</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46229.02597222223</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75c847b7-d158-4b60-9593-4b018a26ec7b              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e3c51c13-4454-402e-af99-8ea23f8ffa73              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Hi there. 129 745</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23301648</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>447429947231</v>
+      </c>
+      <c r="F14" t="n">
+        <v>234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46229.02434027778</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46229.02436342592</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46229.02458333333</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206cc130-7d66-4137-8439-f37f5294782f              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d058954c-18d7-4f77-8673-42558266495e              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Hi there. 116 992</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>21 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23301647</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>447413420387</v>
+      </c>
+      <c r="F15" t="n">
+        <v>234</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46229.02424768519</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46229.02427083333</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46229.02442129629</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83872522-5fcb-4a5f-a8f8-253dfada2036              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">802a4733-9fd0-45b3-a8a3-6e5600348e0d              </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Hi there. 065 117</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23301646</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>447545045417</v>
+      </c>
+      <c r="F16" t="n">
+        <v>234</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46229.0234837963</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46229.02350694445</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46229.02376157408</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64ce2a7d-8ddc-4610-8192-480498dd97ee              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8bf1b7e5-87d4-4225-9119-373476a05d34              </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Hi there. 585 746</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>24 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23301645</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>447711918383</v>
+      </c>
+      <c r="F17" t="n">
+        <v>234</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46229.02217592593</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46229.02219907408</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46229.02233796296</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2f95d4a2-72d9-4ef5-9553-dace9b94083c              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4d3b9853-ccb9-44ab-a159-f0c0ae0047ce              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Hi there. 532 849</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23301644</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>447452878738</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46229.02120370371</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46229.02126157407</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46229.02148148148</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ef63cca9-6336-44bd-948e-1c95b2c67d28              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45c1e354-de35-42a3-ab08-431a3cffeb06              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Hi there. 563 348</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>24 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23301643</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>447943854558</v>
+      </c>
+      <c r="F19" t="n">
+        <v>234</v>
+      </c>
+      <c r="G19" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46229.01961805556</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46229.0196412037</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46229.01976851852</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6bf50da7-1aaa-4e63-a150-914fbe44663a              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15454314-bbf5-4f39-977e-7dadaf3e4e76              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Hi there. 252 377</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23301642</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>51917313584</v>
+      </c>
+      <c r="F20" t="n">
+        <v>716</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46229.01913194444</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46229.01916666667</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46229.01917824074</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b70f84d2-273e-4bec-9efb-2290b91158be              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dea1ac92-0c42-4a5a-ab10-1f02a64ceb55              </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 5524
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>4 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23301641</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>50491528305</v>
+      </c>
+      <c r="F21" t="n">
+        <v>708</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46229.01673611111</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46229.01674768519</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46229.01703703704</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6584308-dcfc-4270-87cc-968a037b6703              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b24a7084-fede-4b62-bbdf-8603882bd530              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 4937168</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>26 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23301640</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>447455330730</v>
+      </c>
+      <c r="F22" t="n">
+        <v>234</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46229.014375</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46229.01440972222</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46229.01449074074</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251b47e7-95d6-49a4-98a7-ae73f10abeae              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2c2235bf-5ce5-4342-896c-4c8f5e810862              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Hi there. 651 301</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23301639</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>447446009850</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46229.01435185185</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46229.01438657408</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>46229.01454861111</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ab3d7503-515b-48d7-87f0-9af30e940bfe              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">746d82ed-16ed-4c37-bb98-f20c049a4423              </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Hi there. 808 120</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23301638</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>51946093657</v>
+      </c>
+      <c r="F24" t="n">
+        <v>716</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ENTEL(ex NEXTEL DEL PERU S.A)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46229.01339120371</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46229.01344907407</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46229.01344907407</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a6101e3b-146d-4354-af16-2885757d2cc1              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76a3ec43-23e2-4108-bc7f-90bf1dbb9da6              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 7753
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>5 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23301637</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>447576811670</v>
+      </c>
+      <c r="F25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46229.0124074074</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46229.01243055556</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46229.0127199074</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ed07ad4a-3ccc-4efe-a6d0-bc5c947aac68              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83be00f4-b1ad-4246-bb6d-7c53d6828ab5              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Hi there. 492 140</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>27 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23301636</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>447970721940</v>
+      </c>
+      <c r="F26" t="n">
+        <v>234</v>
+      </c>
+      <c r="G26" t="n">
+        <v>33</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46229.01190972222</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46229.01193287037</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>46229.0121412037</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b92378f1-8412-4f72-82eb-a0df96b322d8              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6b1e763-1261-4bef-8db2-d7bc06936b9a              </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Hi there. 779 087</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23301635</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>447727026802</v>
+      </c>
+      <c r="F27" t="n">
+        <v>234</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46229.01020833333</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46229.01023148148</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46229.01041666666</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d101b9b5-fa1c-4146-9008-a76aaaad9e58              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7434523c-9d5b-4d84-9fd2-0b8cc191918b              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Hi there. 082 707</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23301634</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>50496546446</v>
+      </c>
+      <c r="F28" t="n">
+        <v>708</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Undeliverable</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46229.00940972222</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46229.00943287037</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46229.00953703704</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a6ef421-83fd-4506-83f3-2ecba27d6453              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dd8ae306-373e-4214-85b1-731eec8bd234              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Twitch es: 568089</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23301633</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>447772106131</v>
+      </c>
+      <c r="F29" t="n">
+        <v>234</v>
+      </c>
+      <c r="G29" t="n">
+        <v>33</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>46229.00902777778</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>46229.00905092592</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>46229.00923611111</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5a60e3e-887b-43b2-815f-feb6ef8a1573              </t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2570fe1c-30ce-4a79-966e-4ef4fcdac9d6              </t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Hi there. 577 652</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23301632</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>447833645300</v>
+      </c>
+      <c r="F30" t="n">
+        <v>234</v>
+      </c>
+      <c r="G30" t="n">
+        <v>15</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>46229.00846064815</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>46229.00849537037</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>46229.00871527778</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83905199-980b-4391-b9ef-8e980a3eb8e1              </t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a62735d0-9f0c-491e-8196-43f2e3dd54bb              </t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Hi there. 539 917</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>22 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>23301631</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>447483292119</v>
+      </c>
+      <c r="F31" t="n">
+        <v>234</v>
+      </c>
+      <c r="G31" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>46229.00813657408</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>46229.00815972222</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>46229.00831018519</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234e5a13-8227-47fe-b0ff-d8102fb749f1              </t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52e25fcb-0840-400e-b3fb-d0439fe4b4b9              </t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Hi there. 556 517</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>23301630</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>50491814900</v>
+      </c>
+      <c r="F32" t="n">
+        <v>708</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>46229.00614583334</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>46229.00615740741</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>46229.00634259259</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9e102d7c-40ed-45ae-a331-a96bad93517a              </t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b5fa32a9-eabf-4a1d-9c1f-8ca6ef6cfd30              </t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 1922304</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>23301629</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>447308604515</v>
+      </c>
+      <c r="F33" t="n">
+        <v>234</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>46229.00574074074</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>46229.00576388889</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>46229.00586805555</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97011040-b386-42ab-88cb-0fd6a6913d93              </t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baba8b22-4f59-4261-aafb-46aabf0baf73              </t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Hi there. 985 505</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>23301628</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>447308604515</v>
+      </c>
+      <c r="F34" t="n">
+        <v>234</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>46229.00549768518</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>46229.00553240741</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>46229.00572916667</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d429bf83-c277-4746-ae20-934bfa9cc5d9              </t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">650651c0-17dd-45d6-8fa2-c443e3f73994              </t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Hi there. 182 207</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>20 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>23301627</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>50497407890</v>
+      </c>
+      <c r="F35" t="n">
+        <v>708</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>46229.0053125</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>46229.00533564815</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46229.00542824074</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d94006d4-9200-4e99-bd34-32a088d0a3a2              </t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ac62c0d0-5859-4fc5-948d-e192d8a0e766              </t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 5826011</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>10 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>23301626</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>50497407890</v>
+      </c>
+      <c r="F36" t="n">
+        <v>708</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>46229.00412037037</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>46229.0041550926</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46229.00430555556</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ac148f5-a119-43eb-b6b7-8c39f233b458              </t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a652bd8f-e5bc-4f09-8d03-072a88518ba7              </t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 2682695</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>23301625</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>447383302727</v>
+      </c>
+      <c r="F37" t="n">
+        <v>234</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>46229.00293981482</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>46229.00295138889</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46229.00311342593</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a827339a-2f89-417d-8cde-880351788ebb              </t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">706ecd79-af83-44fb-9acc-7a9b5d9eaf31              </t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Hi there. 129 304</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>23301624</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>447483292119</v>
+      </c>
+      <c r="F38" t="n">
+        <v>234</v>
+      </c>
+      <c r="G38" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>46229.00195601852</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>46229.00197916666</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>46229.00223379629</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da996341-e8fd-45c2-b4df-0ba79796debe              </t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ebd4fe8-d225-4934-8fc3-cec06c5ac7fe              </t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Hi there. 585 925</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>24 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>23301623</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>447365410266</v>
+      </c>
+      <c r="F39" t="n">
+        <v>234</v>
+      </c>
+      <c r="G39" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>46229.00190972222</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>46229.00193287037</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>46229.00217592593</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93de168c-81ce-47bb-8bbb-895fe61aeb21              </t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98799c0f-1894-4f5b-8e0a-ee27a7d45bd2              </t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Hi there. 045 878</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>23301622</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>50498009332</v>
+      </c>
+      <c r="F40" t="n">
+        <v>708</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>46229.00084490741</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>46229.00086805555</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>46229.00128472222</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29eb5bd1-0a73-42e5-97ae-4d0cd113aa37              </t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ae669255-c1b3-41aa-99fe-a3f69342ff2f              </t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 4604392</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>38 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,7718 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23307705</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447891493656</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46230.04042824074</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46230.04045138889</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46230.04063657407</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40801faf-2ba7-4e67-a352-2ce9063316ad              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7f08332f-b5f4-4f4b-819e-fe77c6cea2f2              </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 162 819</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23307704</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>447813093371</v>
+      </c>
+      <c r="F3" t="n">
+        <v>234</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46230.03888888889</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46230.03891203704</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46230.03907407408</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81140810-0cc2-4378-979d-0b466abdb2c2              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ee1cd6fc-6c13-4436-96b0-85425dda6c78              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Hi there. 298 574</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23307703</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447580094909</v>
+      </c>
+      <c r="F4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46230.03714120371</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46230.03716435185</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46230.03733796296</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d28b91c8-f686-42bd-a5c6-c28ff89b22f5              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bec67411-a98a-49ed-b65e-1d0fd7f054d7              </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hi there. 725 437</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23307702</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447813093371</v>
+      </c>
+      <c r="F5" t="n">
+        <v>234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46230.03665509259</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46230.03667824074</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46230.03684027777</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7f0f8e70-3da3-4f65-b204-340866beac8d              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cc0360c8-2fda-47f2-8dfd-2f2c53bec468              </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Hi there. 262 076</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23307701</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>447429264850</v>
+      </c>
+      <c r="F6" t="n">
+        <v>234</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46230.03616898148</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46230.03619212963</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46230.03634259259</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3dd64d60-9519-4b9e-98b6-db534bb4a518              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dc11eafb-9372-4187-aa16-6f7c4886952d              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Hi there. 084 507</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23307700</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50499492735</v>
+      </c>
+      <c r="F7" t="n">
+        <v>708</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46230.0352199074</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46230.03523148148</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46230.03537037037</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caf64b73-0dac-4cd8-931a-508f58378065              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f8eb5396-c317-452f-88d8-7671d5b2f4e9              </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Twitch es: 343102</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23307699</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447727656941</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46230.03451388889</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46230.03456018519</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46230.03472222222</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bb7e0024-89d0-46c1-81a4-20967f39ba96              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85469187-df22-4a07-a62e-1932f745f652              </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 216 138</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23307698</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447972318798</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46230.03319444445</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46230.03320601852</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46230.03337962963</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2dd486d5-649c-4065-a502-c547e6a2c971              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9220ffb1-9d92-4c7c-adb1-9d53531a1b28              </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 620 498</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23307697</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>447450673132</v>
+      </c>
+      <c r="F10" t="n">
+        <v>234</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46230.03315972222</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46230.03318287037</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46230.03335648148</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98d21f76-5cb2-483b-a07c-08f5d71e745c              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5342d8c-5fec-40df-a519-1e6457de946e              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Hi there. 005 098</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23307696</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>447590417732</v>
+      </c>
+      <c r="F11" t="n">
+        <v>234</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46230.03049768518</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46230.03050925926</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46230.0306712963</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">994378d5-9416-4812-8ff1-f3cf3548ae55              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62e5306f-9a5a-4463-9226-6bbabf066df8              </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Hi there. 550 117</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23307695</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447828499386</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46230.03043981481</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46230.03045138889</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46230.03061342592</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0463ef73-2d5e-47ba-9a82-6f4f1c29e799              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dffe33a9-5263-4319-9d15-5f7c33864380              </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 842 567</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23307694</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50498183765</v>
+      </c>
+      <c r="F13" t="n">
+        <v>708</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46230.02981481481</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46230.02982638889</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>46230.02994212963</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ced325f2-2a28-4e48-8175-a3d4e819ebbd              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33791794-e3ac-4603-bf78-f7bbcfd1703e              </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 8939670</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>11 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23307693</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>50498183765</v>
+      </c>
+      <c r="F14" t="n">
+        <v>708</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Undeliverable</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46230.02851851852</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46230.02854166667</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46230.02871527777</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e690cfdd-9682-43d0-8dc9-aa9b94d46651              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f34bdb83-c547-45be-9a55-777c4d62fe00              </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 5675309</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23307692</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>447717116719</v>
+      </c>
+      <c r="F15" t="n">
+        <v>234</v>
+      </c>
+      <c r="G15" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46230.02789351852</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46230.02790509259</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46230.02805555556</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ff72f43-2fec-4e94-834b-9597fc57a1e5              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7c65b95d-e1ac-4450-acf4-bbaca906c251              </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Hi there. 230 673</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23307691</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>447930226588</v>
+      </c>
+      <c r="F16" t="n">
+        <v>234</v>
+      </c>
+      <c r="G16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46230.0275462963</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46230.02758101852</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46230.02775462963</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f3b36fe5-1906-4d04-b8ee-66d6ea7a9c96              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4b281516-b415-4818-af1b-1da830ac6656              </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Hi there. 149 360</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23307690</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>447888365295</v>
+      </c>
+      <c r="F17" t="n">
+        <v>234</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46230.02736111111</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46230.02738425926</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46230.0275462963</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9581bedc-12ab-4cf4-9738-a337d5f676ed              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ec044b13-a13c-4cf6-817b-1f34304a3ce6              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Hi there. 698 502</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23307689</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>447979273327</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46230.02719907407</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46230.02722222222</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46230.02739583333</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b1920868-0029-488a-9403-9fc2a279aa16              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39c82166-f4ab-422b-a677-5520da9dad8b              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Hi there. 403 786</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23307688</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>447916711102</v>
+      </c>
+      <c r="F19" t="n">
+        <v>234</v>
+      </c>
+      <c r="G19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46230.0270949074</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46230.02712962963</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46230.02731481481</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ff195ee2-284c-4bc1-b24a-7cdeb256a4d4              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">742d1f35-6338-49c4-81d3-b02745ccbc93              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Hi there. 696 325</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23307687</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alcyon Cloud SMS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ALCY_HQ_OTP</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ALCY_HQ_OTP</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>51906117844</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MCC/MNC Not Found</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46230.02615740741</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46230.02616898148</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>138</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>1007</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85ab439d-7b09-4a10-87ff-2562c10d9cd7              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; Tu cuenta de WhatsApp esta siendo registrada en un dispositivo nuevo No compartas el codigo con nadie Tu codigo de WhatsApp es: 45144.</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23307686</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>447874618622</v>
+      </c>
+      <c r="F21" t="n">
+        <v>234</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46230.02523148148</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46230.0252662037</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46230.02543981482</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20808e74-dd6c-48d7-a22e-cec9558863e1              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28dfff51-569c-4aae-bdad-b81568d91bd0              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Hi there. 951 117</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23307685</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>447703559162</v>
+      </c>
+      <c r="F22" t="n">
+        <v>234</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46230.02120370371</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46230.02121527777</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46230.02140046296</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4bb8d3c3-66db-46cd-a5af-d04888ba9659              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b0876b55-bb6d-429b-8143-2ad5c084220f              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Hi there. 182 637</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23307684</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>50493505564</v>
+      </c>
+      <c r="F23" t="n">
+        <v>708</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46230.02114583334</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46230.02115740741</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>46230.02128472222</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">766dc4e5-a087-44a9-889c-f50346e0bce1              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24f7e72b-efce-459c-9ba1-f91b886d3ecc              </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 5936062</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>12 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23307683</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>51927290731</v>
+      </c>
+      <c r="F24" t="n">
+        <v>716</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46230.020625</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46230.02070601852</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46230.02071759259</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1b6f64a5-e042-4805-821d-8c9372b2422b              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f4f68332-8760-4be5-a122-d63628053280              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 7647
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>8 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23307682</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>447378129854</v>
+      </c>
+      <c r="F25" t="n">
+        <v>234</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46230.02009259259</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46230.02011574074</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46230.02027777778</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98954862-120d-4247-ae8e-138721f5e263              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2259a57a-3e1d-4d3a-bda5-7d555bc5abf7              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Hi there. 913 848</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23307681</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>50493505564</v>
+      </c>
+      <c r="F26" t="n">
+        <v>708</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46230.01993055556</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46230.0199537037</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>46230.02008101852</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dfcc8cdb-65c9-414b-a7e1-06c77571a5f0              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f4c5110d-1dbe-440e-91cc-c6402ff42666              </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 2214003</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23307680</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>447533592497</v>
+      </c>
+      <c r="F27" t="n">
+        <v>234</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46230.01943287037</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46230.01945601852</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46230.01961805556</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e5319525-5a4b-4efd-84fd-fcec1a108a6c              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cdca08e1-964c-4568-a4e4-ac1714d31251              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Hi there. 427 039</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23307679</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>447599287903</v>
+      </c>
+      <c r="F28" t="n">
+        <v>234</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46230.01670138889</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46230.01672453704</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46230.016875</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65e0795a-72d1-4bf4-be6f-11c461964c7f              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e19cb481-15bd-4179-b205-0f66d367de50              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Hi there. 493 533</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23307678</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>447411257491</v>
+      </c>
+      <c r="F29" t="n">
+        <v>234</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>46230.01645833333</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>46230.01648148148</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>46230.01664351852</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8714d6fb-417a-4482-ad00-f47d8b56253b              </t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e905ccb7-ca96-404f-99a9-95e1a024770c              </t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Hi there. 149 674</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23307677</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>447973252184</v>
+      </c>
+      <c r="F30" t="n">
+        <v>234</v>
+      </c>
+      <c r="G30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>46230.01509259259</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>46230.01512731481</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>46230.01528935185</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6b515a86-3a56-43bc-ba33-8e924d90220a              </t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34dd86d3-5949-4e69-b7fd-a000050d2d39              </t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Hi there. 354 584</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>23307676</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>447427307167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>234</v>
+      </c>
+      <c r="G31" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>46230.01491898148</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>46230.01494212963</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>46230.01511574074</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91743f70-d383-41f8-b2e1-68a9dd478195              </t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">440fa955-03be-4675-bc82-983d843f0b29              </t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Hi there. 934 031</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>23307675</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>447474133380</v>
+      </c>
+      <c r="F32" t="n">
+        <v>234</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>46230.01405092593</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>46230.01407407408</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>46230.01423611111</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55f5d23a-915e-4c51-b939-fef2140fd30e              </t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06373177-f0ef-45e0-aea5-06275ac5c7c9              </t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Hi there. 419 434</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>23307674</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>447310107230</v>
+      </c>
+      <c r="F33" t="n">
+        <v>234</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>46230.01378472222</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>46230.01380787037</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>46230.01398148148</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e39ef21-f215-4e3b-9a65-0b52f91f4076              </t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">364826f3-3de0-4027-a739-9dcc970a3367              </t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Hi there. 203 180</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>23307673</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>447482048101</v>
+      </c>
+      <c r="F34" t="n">
+        <v>234</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>46230.01284722222</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>46230.0128587963</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>46230.01302083334</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b1911576-95f2-41fe-869f-6004220862d6              </t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">453d0879-2e5b-4527-9294-5b97d6f2aeb3              </t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Hi there. 316 575</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>23307672</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>59175920717</v>
+      </c>
+      <c r="F35" t="n">
+        <v>736</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>AIRBNB</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>46230.01201388889</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>46230.01202546297</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>46230.01217592593</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e848dc78-e123-4a4e-a82b-70bbb8decd6a              </t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8744d3d8-a843-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Airbnb es 929187.</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>23307671</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>447482048101</v>
+      </c>
+      <c r="F36" t="n">
+        <v>234</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>46230.01180555556</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>46230.01181712963</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46230.01197916667</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a02fda5a-7f7e-4bb7-9c9c-f48e087879a3              </t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">563a00c8-2bc0-4f15-abc4-9a38089564e3              </t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Hi there. 817 271</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>23307670</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>447423492749</v>
+      </c>
+      <c r="F37" t="n">
+        <v>234</v>
+      </c>
+      <c r="G37" t="n">
+        <v>15</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>46230.01114583333</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>46230.01116898148</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46230.01133101852</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ee2e4519-d744-4a54-af3a-ed90fe73d314              </t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cddce191-813e-4fee-aaf2-4a12612a0684              </t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Hi there. 921 038</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>23307669</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>447710454969</v>
+      </c>
+      <c r="F38" t="n">
+        <v>234</v>
+      </c>
+      <c r="G38" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>46230.01078703703</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>46230.01081018519</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>46230.0109837963</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3c3ad8ab-a841-41cb-a129-82e755b12e8f              </t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fe4d731e-7fdd-40e4-b6e1-2a1fc9eb3c7d              </t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Hi there. 971 931</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>23307668</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>59177944733</v>
+      </c>
+      <c r="F39" t="n">
+        <v>736</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>AIRBNB</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>46230.01056712963</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>46230.01059027778</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>46230.01064814815</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6546347-f689-487c-a90e-8691240dc27e              </t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3d868178-a843-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Tú código de verificación de Airbnb es: 9404.</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>23307667</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>447767768642</v>
+      </c>
+      <c r="F40" t="n">
+        <v>234</v>
+      </c>
+      <c r="G40" t="n">
+        <v>15</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>46230.01013888889</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>46230.01016203704</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>46230.0103125</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e4713b0c-85fb-4d10-8c35-cf52814a0a9e              </t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d216f863-e02f-4211-9353-a14f30ec085d              </t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Hi there. 845 224</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>23307666</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>447481851611</v>
+      </c>
+      <c r="F41" t="n">
+        <v>234</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>46230.00997685185</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>46230.00998842593</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46230.01017361111</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26ec1e7d-99c2-4591-b38f-6320ab110464              </t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6c797092-59ec-44f7-9bd3-07fcde9bd9c6              </t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Hi there. 344 323</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>23307665</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>447789114517</v>
+      </c>
+      <c r="F42" t="n">
+        <v>234</v>
+      </c>
+      <c r="G42" t="n">
+        <v>15</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>VODAFONE LIMITED</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>46230.00989583333</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>46230.00990740741</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>46230.01009259259</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2f26c8f2-4af1-416f-9792-d415d9d86fac              </t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8f9b8692-bb5c-41d1-a2f0-93765c0f9605              </t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Hi there. 451 168</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>23307664</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>447375492569</v>
+      </c>
+      <c r="F43" t="n">
+        <v>234</v>
+      </c>
+      <c r="G43" t="n">
+        <v>30</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>46230.00981481482</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>46230.00982638889</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>46230.00997685185</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d4f3d319-c8aa-4b3f-ba69-9b846f403eac              </t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e1a83db4-0001-426b-89e7-de5e746420b8              </t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Hi there. 579 484</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>14 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>23307663</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>447576609243</v>
+      </c>
+      <c r="F44" t="n">
+        <v>234</v>
+      </c>
+      <c r="G44" t="n">
+        <v>20</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>46230.00791666667</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>46230.00793981482</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>46230.00810185185</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5571652d-6d8c-4cbc-bb74-9cf845d8f4b6              </t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27e663ae-229f-4e47-a619-c016f0f2a475              </t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Hi there. 182 578</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>23307662</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5585991870987</v>
+      </c>
+      <c r="F45" t="n">
+        <v>724</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>myGiGroup</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>46230.00758101852</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>46230.00759259259</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>46230.00778935185</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f8ac3914-6c65-41a2-a026-321949c49d7c              </t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a2e4fcc4-a842-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Your myGiGroup access code is 708640</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>23307661</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>447528809222</v>
+      </c>
+      <c r="F46" t="n">
+        <v>234</v>
+      </c>
+      <c r="G46" t="n">
+        <v>33</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>46230.00745370371</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>46230.00747685185</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>46230.00762731482</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4504c552-9d9b-4f3c-8524-cbed9e718a4b              </t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a8150e0a-3965-4190-8069-1e83a7176852              </t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Hi there. 748 092</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>23307660</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>447738825268</v>
+      </c>
+      <c r="F47" t="n">
+        <v>234</v>
+      </c>
+      <c r="G47" t="n">
+        <v>10</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>46230.00589120371</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>46230.00591435185</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>46230.00606481481</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153992ab-108c-4986-9424-a4b78dc108cf              </t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0289a0be-0d25-4ee2-a7ad-fb8b9a117188              </t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Hi there. 713 011</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>23307659</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>447882129456</v>
+      </c>
+      <c r="F48" t="n">
+        <v>234</v>
+      </c>
+      <c r="G48" t="n">
+        <v>20</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>46230.00530092593</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>46230.00532407407</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>46230.00547453704</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48917a7d-35c2-4254-9f61-4d757a3e0b7f              </t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01363c88-90a1-4981-accc-4b1c537fe099              </t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Hi there. 999 676</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>23307658</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>447453277212</v>
+      </c>
+      <c r="F49" t="n">
+        <v>234</v>
+      </c>
+      <c r="G49" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>46230.00413194444</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>46230.00414351852</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>46230.00431712963</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a46cfb0f-d723-46e7-a4ce-aeb4d708d25c              </t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37f8d955-385b-4703-bd2e-0268ce9b9684              </t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Hi there. 772 213</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>16 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>23307657</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5511913591178</v>
+      </c>
+      <c r="F50" t="n">
+        <v>724</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>46230.00388888889</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>46230.00390046297</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>46230.00408564815</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e7ced09f-b6ad-47d9-856f-961c30515605              </t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e4b33a40-a841-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>Seu codigo de verificacao da Choice Hotels: 693496. Nao compartilhe.</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>23307656</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>447482048101</v>
+      </c>
+      <c r="F51" t="n">
+        <v>234</v>
+      </c>
+      <c r="G51" t="n">
+        <v>20</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>46230.0036574074</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>46230.00366898148</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>46230.00383101852</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2356c3a5-e262-441c-a45b-b9498463286b              </t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c50d531b-3943-4328-811a-acf19c577d8b              </t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Hi there. 801 937</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>23307655</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>447828960186</v>
+      </c>
+      <c r="F52" t="n">
+        <v>234</v>
+      </c>
+      <c r="G52" t="n">
+        <v>20</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>46230.00287037037</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>46230.00289351852</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>46230.00304398148</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9b165087-c65a-43fc-b37c-4195fdb04b0c              </t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3290b524-49de-426d-93e6-24a3e46f620c              </t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Hi there. 212 211</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>23307654</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>51916582307</v>
+      </c>
+      <c r="F53" t="n">
+        <v>716</v>
+      </c>
+      <c r="G53" t="n">
+        <v>15</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>VIETTEL PERU S.A.C.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ALCYON_HQ</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>46230.0025</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>46230.00253472223</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>46230.00253472223</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Latin1</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a0d96ca6-35fd-4396-b7fd-3944faa416db              </t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c553ca2e-ac76-438b-b3bf-0b06e7a9d4cc              </t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; inDrive code: 6021
+cpjyScQ++Hg</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>3 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>23307653</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>50497046083</v>
+      </c>
+      <c r="F54" t="n">
+        <v>708</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>46230.00196759259</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>46230.00199074074</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>46230.0021412037</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b1f73614-6c78-418e-b4f5-d56c984dfff8              </t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc9aaada-490f-480f-83e4-9aff6d1b7cd8              </t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Twitch es: 256294</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>23307652</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>447828960186</v>
+      </c>
+      <c r="F55" t="n">
+        <v>234</v>
+      </c>
+      <c r="G55" t="n">
+        <v>20</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>46230.00159722222</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>46230.00160879629</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>46230.00177083333</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a4993f61-66f8-4932-9c71-eb9c0fc89ea6              </t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6a09744c-b285-4b15-9203-06f9b27463bc              </t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Hi there. 310 683</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>15 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>23307651</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>50497046083</v>
+      </c>
+      <c r="F56" t="n">
+        <v>708</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>46230.0002662037</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>46230.00030092592</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>46230.00063657408</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2186747f-3b65-4d0d-82da-687aa697c7a6              </t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">830c30d7-1148-4f7b-88f6-9b2c642efb41              </t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Twitch es: 407660</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>32 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>23307650</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>447865379332</v>
+      </c>
+      <c r="F57" t="n">
+        <v>234</v>
+      </c>
+      <c r="G57" t="n">
+        <v>20</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>T2W_SIM</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>46230.00016203704</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>46230.00018518518</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>46230.00035879629</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">510d05cb-e229-4d41-b96f-398ad6bc6ea2              </t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e48cf00c-c05b-4e82-8e47-2e3a8ea1ac19              </t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Hi there. 162 212</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
         </is>
       </c>
     </row>

--- a/datos/live_today.xlsx
+++ b/datos/live_today.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +601,5420 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>23321734</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>447968138945</v>
+      </c>
+      <c r="F2" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>EE Limited (Orange)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>46231.02224537037</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>46231.02228009259</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7c49307c-5fb9-4e31-9a41-6ea61d59efb7              </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Hi there. 081 138</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>23321733</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5521969239890</v>
+      </c>
+      <c r="F3" t="n">
+        <v>724</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CUBIC TELECOM BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>myGiGroup</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>46231.02214120371</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>46231.02217592593</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46231.02234953704</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7b5223e0-d40b-41f4-ba7f-6b27e0170210              </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc7db5f8-a90e-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Your myGiGroup access code is 085517</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>18 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23321732</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447944377257</v>
+      </c>
+      <c r="F4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>46231.02144675926</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>46231.02146990741</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d5c712e4-8603-4313-865b-a2d4c067905a              </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hi there. 076 943</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>23321731</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>447389033332</v>
+      </c>
+      <c r="F5" t="n">
+        <v>234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>46231.02030092593</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>46231.02033564815</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25610cc7-a54e-4b44-b054-ff226af3dc6e              </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Hi there. 166 076</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23321730</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5541987815048</v>
+      </c>
+      <c r="F6" t="n">
+        <v>724</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CLARO S.A.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Eneba</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>46231.01989583333</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>46231.01991898148</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46231.01998842593</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1cc48bf0-78a7-4deb-acc9-4b35d0a2960c              </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4833a824-a90e-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Use o codigo 395894 para validar as suas acoes no eneba.com</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>8 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>23321729</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>447474990280</v>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>46231.0196412037</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>46231.01965277778</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">adbec2ca-3d25-4e32-a02b-98cde6e17502              </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Hi there. 121 703</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>23321728</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>447846464004</v>
+      </c>
+      <c r="F8" t="n">
+        <v>234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>46231.01954861111</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>46231.01958333333</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aa0ad6fe-9cdf-4cf9-a9b6-b0df2cf148e9              </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hi there. 408 265</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>23321727</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>447862997982</v>
+      </c>
+      <c r="F9" t="n">
+        <v>234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>46231.01938657407</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>46231.0194212963</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ee603bc5-d376-4588-91b0-89f6fe70cae4              </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Hi there. 588 546</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>23321726</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PTG_DIR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PSG_DIR</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5575993000755</v>
+      </c>
+      <c r="F10" t="n">
+        <v>724</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CUBIC TELECOM BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>KPERU_HQ</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>SUPERPROF</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46231.01675925926</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>46231.01677083333</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46231.01697916666</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>144</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a50443a7-161b-4e82-a739-5b54455bcc46              </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a6045c58-a90d-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>O codigo para validar seu telefone na SUPERPROF é: 1658. Conecte-se em seu perfil ou clique em https://superprof.com.br/44285845s1658m6320384160</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>19 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>23321725</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>56997423738</v>
+      </c>
+      <c r="F11" t="n">
+        <v>730</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Telefonica Moviles Chile sa (brand movistar)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PTG_MKT_OUT</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>enjoycl</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>46231.01490740741</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>46231.01493055555</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46231.01497685185</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9b606f36-6936-4141-a2ca-03febdf4c8a6              </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5dc6fa7a08044a0a0951185a4bf6dc9                  </t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[ENJOYCL] Gracias por unirte a enjoycl.com.  Haz tu primer deposito y recibe hasta 30% de bono.</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>6 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>23321724</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>447725504817</v>
+      </c>
+      <c r="F12" t="n">
+        <v>234</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>46231.01358796296</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>46231.01362268518</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">641e27e8-e33c-445c-b7ee-b9cd66888647              </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Hi there. 970 776</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23321723</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>447491339907</v>
+      </c>
+      <c r="F13" t="n">
+        <v>234</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>46231.01346064815</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>46231.0134837963</v>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2524b29b-f11d-4469-a314-1aee15afeccb              </t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Hi there. 973 792</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23321722</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>447491339907</v>
+      </c>
+      <c r="F14" t="n">
+        <v>234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>46231.01319444444</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>46231.01321759259</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03e03890-42de-4918-937b-7d6c9eaf0196              </t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Hi there. 641 309</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23321721</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>447402941470</v>
+      </c>
+      <c r="F15" t="n">
+        <v>234</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>46231.01263888889</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>46231.01267361111</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69fa8cb0-a692-476d-92b1-3bb17c3c8a54              </t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Hi there. 321 116</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>23321720</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>447861660556</v>
+      </c>
+      <c r="F16" t="n">
+        <v>234</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>46231.01238425926</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>46231.01243055556</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cb72f495-e840-4e61-8fe5-7b9712379850              </t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Hi there. 307 535</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>23321719</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>59176640120</v>
+      </c>
+      <c r="F17" t="n">
+        <v>736</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>46231.01201388889</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>46231.01202546297</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>46231.01216435185</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>79</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62416989-1af9-4411-98ea-96c8caaecd89              </t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b210cb9c-a90c-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>&lt;#&gt; Codigo de WhatsApp: 846-459
+No compartas este codigo con nadie.
+4sgLq1p5sV6</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>13 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>23321718</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>59178530188</v>
+      </c>
+      <c r="F18" t="n">
+        <v>736</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>46231.01138888889</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>46231.01140046296</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46231.0114699074</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5d8a2d91-b8a8-4f04-b1ec-7de8f2c71479              </t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91ed200c-a90c-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Cuentas de Twitch vinculadas a tu número de teléfono: 820arthur</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>23321717</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59177917956</v>
+      </c>
+      <c r="F19" t="n">
+        <v>736</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>AIRBNB</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>46231.01135416667</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>46231.01136574074</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>46231.01155092593</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89d3aaed-07bd-4dc8-b929-c613bc7184c6              </t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901f87d0-a90c-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Airbnb es 0113.</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>17 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>23321716</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>50497405535</v>
+      </c>
+      <c r="F20" t="n">
+        <v>708</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>46231.01128472222</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>46231.0112962963</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46231.01172453703</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">084bb430-16ad-4bef-a744-78d7d53175f0              </t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e68439b3-bc3a-4796-bea2-2c7c2fff27a3              </t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>uridad, no utilices este código fuera de Docusign. No compartas nun</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>38 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>23321716</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>50497405535</v>
+      </c>
+      <c r="F21" t="n">
+        <v>708</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>46231.01128472222</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>46231.0112962963</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46231.01172453703</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ce1831e-a58c-4c01-9444-7f02ea8e9d3a              </t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">661ba999-a31d-46c3-af1e-684035b6929d              </t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ca este código con nadie.</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>38 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>23321716</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>50497405535</v>
+      </c>
+      <c r="F22" t="n">
+        <v>708</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>46231.01128472222</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>46231.0112962963</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>46231.01172453703</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9665efa1-6570-4058-8c26-76af8696624f              </t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a34667b7-b513-442e-8830-026a32aa72a4              </t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Docusign es 629604. Por motivos de seg</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>38 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23321715</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>447429657697</v>
+      </c>
+      <c r="F23" t="n">
+        <v>234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>46231.01100694444</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>46231.01101851852</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0eca3c85-1a35-4833-9496-abda959770a8              </t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Hi there. 985 075</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23321714</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>50494577724</v>
+      </c>
+      <c r="F24" t="n">
+        <v>708</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Undeliverable</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>46231.010625</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>46231.01063657407</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46231.01068287037</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c43b7302-9dd9-422a-b428-436373d28945              </t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44626975-51eb-4e62-afb4-6a0b4c17f5b9              </t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Twitch es: 359890</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>5 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23321713</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>59178530188</v>
+      </c>
+      <c r="F25" t="n">
+        <v>736</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Telecel</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>KITE_WHS</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>46231.01017361111</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>46231.01019675926</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>46231.01025462963</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9e327c62-eb48-4522-8791-394ac0fc7e23              </t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5381179c-a90c-01f2-b75e-9c6b003e96d8              </t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Cuentas de Twitch vinculadas a tu número de teléfono: 820arthur</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>7 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23321712</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>447311809124</v>
+      </c>
+      <c r="F26" t="n">
+        <v>234</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>46231.01013888889</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>46231.01017361111</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0516bf57-7f0e-44fe-8eb4-a8f09dcee1c9              </t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Hi there. 508 265</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23321711</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>50497405535</v>
+      </c>
+      <c r="F27" t="n">
+        <v>708</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>46231.00973379629</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>46231.00974537037</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>46231.01</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18463634-6367-45e2-b0a3-dfa74375c075              </t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d6128c31-f61a-4a21-a504-58a68113fb2f              </t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Tu código de verificación de Docusign es 373113. Por motivos de seg</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23321711</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>50497405535</v>
+      </c>
+      <c r="F28" t="n">
+        <v>708</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>46231.00973379629</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>46231.00974537037</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>46231.01</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7d13c262-9ade-4078-a28e-93d1cb5886c3              </t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113af3f2-e787-44c1-890d-66abc7a5260c              </t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>uridad, no utilices este código fuera de Docusign. No compartas nun</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23321711</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>50497405535</v>
+      </c>
+      <c r="F29" t="n">
+        <v>708</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>46231.00973379629</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>46231.00974537037</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>46231.01</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2b447421-943b-4ee5-9190-c4242f6e447f              </t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">af8476d7-324e-45cd-8597-d45b6a0a6129              </t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ca este código con nadie.</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>23 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>23321710</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>447886968987</v>
+      </c>
+      <c r="F30" t="n">
+        <v>234</v>
+      </c>
+      <c r="G30" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>46231.00907407407</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>46231.00909722222</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ebeb131-d042-4c70-a067-cf4f2625a011              </t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Hi there. 168 942</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>23321709</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>447707742924</v>
+      </c>
+      <c r="F31" t="n">
+        <v>234</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>46231.00907407407</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>46231.00909722222</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5bf4ffd3-464c-41e1-9858-38ce0fdfc49f              </t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Hi there. 915 056</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>23321708</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>447563305377</v>
+      </c>
+      <c r="F32" t="n">
+        <v>234</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Telefonica UK Limited</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>46231.00858796296</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>46231.00861111111</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1d84b8cc-5cab-4c2c-a247-3aea7320850a              </t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Hi there. 193 222</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>23321707</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>447411425896</v>
+      </c>
+      <c r="F33" t="n">
+        <v>234</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>46231.00810185185</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>46231.008125</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5015b774-2625-46e5-a7fb-fae928f6dbda              </t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Hi there. 399 842</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>23321706</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>447429481804</v>
+      </c>
+      <c r="F34" t="n">
+        <v>234</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>46231.00633101852</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>46231.00636574074</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">892a1c85-2493-4968-85fa-521090515e36              </t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Hi there. 663 242</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>23321705</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>447944377257</v>
+      </c>
+      <c r="F35" t="n">
+        <v>234</v>
+      </c>
+      <c r="G35" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>46231.00557870371</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>46231.00561342593</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ef415af6-edbc-4203-b603-5d48bbf2af26              </t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Hi there. 286 684</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>23321704</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>447868775644</v>
+      </c>
+      <c r="F36" t="n">
+        <v>234</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>46231.00548611111</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>46231.00549768518</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0a315cb0-7f60-4b61-8805-290c8367500d              </t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Hi there. 746 861</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>23321703</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>40779218341</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>MCC/MNC Not Found</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>AOL</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>46231.0045949074</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>46231.0045949074</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>1007</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1f1a1215-bfd6-4cd3-be27-5afb12aa1169              </t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>AOL: If anyone asks you for this code, it's a scam. Your 6-digit code is: 938814</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>23321702</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>447877053090</v>
+      </c>
+      <c r="F38" t="n">
+        <v>234</v>
+      </c>
+      <c r="G38" t="n">
+        <v>20</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>46231.00431712963</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>46231.00434027778</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0eabd443-1189-4417-9b71-b6d6f6a386de              </t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Hi there. 903 525</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>23321701</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ITNIO TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ITNIO_DIR</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>56937230644</v>
+      </c>
+      <c r="F39" t="n">
+        <v>730</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>WOM sa (Novator Partners)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>TCS_MKT</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>enjoycl</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>46231.00327546296</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>46231.00329861111</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>46231.00331018519</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4e047da0-8c12-409a-89d9-5fcda41bb131              </t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81ad03e6-e08b-45cb-9fe7-5da68ca715c7              </t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[ENJOYCL] Gracias por unirte a enjoycl.com.  Haz tu primer deposito y recibe hasta 30% de bono.</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>3 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>23321700</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>447956457476</v>
+      </c>
+      <c r="F40" t="n">
+        <v>234</v>
+      </c>
+      <c r="G40" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>EE Limited ( TM)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>46231.00319444444</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>46231.0032175926</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">581a2775-3113-4edf-bf08-f41d6506d4c8              </t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Hi there. 177 222</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>23321699</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PTG_SIM</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>447462576547</v>
+      </c>
+      <c r="F41" t="n">
+        <v>234</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Hutchison 3G UK Ltd</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Route Not Found In Manual Routing (Reroute)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>46231.00208333333</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>46231.00211805556</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>1015</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f6888cc9-5e5c-4edb-bf41-ced628e76f4e              </t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NR                                                </t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Hi there. 437 518</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>0 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>23321698</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pacific Telecom Group S.A.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PTG_HQ</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>50495684941</v>
+      </c>
+      <c r="F42" t="n">
+        <v>708</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Telefonica Celular S.A (CELTEL) (TIGO)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ASMSC_OK</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>T2W_HQ</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>46231.00010416667</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>46231.00012731482</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>46231.00045138889</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SMPP</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>UCS2</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ad089fd5-da84-4b4f-8b90-4f64220520e3              </t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b4d1c6a6-2a6e-43ea-b46a-8466cb69bbe5              </t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Your Twitch verification code is: 242423</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>30 seconds</t>
         </is>
       </c>
     </row>
